--- a/financial-statements/daivbharathi-technologies-llp/Daivbharathi_Technologies_LLP_Financials_FY_2025-26.xlsx
+++ b/financial-statements/daivbharathi-technologies-llp/Daivbharathi_Technologies_LLP_Financials_FY_2025-26.xlsx
@@ -13,20 +13,20 @@
     <sheet name="BS" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="PL" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="2.1" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="2.2 - 2.10" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="2.11-2.12" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="2.2 - 2.11" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="2.12-2.13" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Flags" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">'2.1'!$A$1:$E$30</definedName>
-    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'2.11-2.12'!$A$1:$E$43</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'2.2 - 2.10'!$B$1:$E$105</definedName>
-    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">'2.2 - 2.10'!$1:$6</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">BS!$A$1:$E$46</definedName>
-    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Flags!$A$1:$D$24</definedName>
+    <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'2.12-2.13'!$A$1:$E$45</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">'2.2 - 2.11'!$B$1:$E$109</definedName>
+    <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Titles" vbProcedure="false">'2.2 - 2.11'!$1:$6</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">BS!$A$1:$E$47</definedName>
+    <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">Flags!$A$1:$D$26</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Master!$A$1:$E$42</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">PL!$A$1:$E$42</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">TB!$A$1:$J$79</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">TB!$A$1:$L$79</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="363">
   <si>
     <t xml:space="preserve">Name of the LLP</t>
   </si>
@@ -175,7 +175,7 @@
     <t xml:space="preserve">Yellow cells = information not available in the Trial Balance; to be filled in before finalisation. All other cells are as per the Tally Trial Balances or derived by formula.</t>
   </si>
   <si>
-    <t xml:space="preserve">Trial Balance (closing balances as per Tally) - mapping to Financial Statements</t>
+    <t xml:space="preserve">Trial Balance (closing balances as per Tally) - mapping to Financial Statements; columns K-L tie each FY 2025-26 balance to the Tally ledger dump</t>
   </si>
   <si>
     <t xml:space="preserve">Totals of rows 7 to 75 (insert new ledger rows above row 76)</t>
@@ -214,6 +214,12 @@
     <t xml:space="preserve">Head (Financial Statement caption)</t>
   </si>
   <si>
+    <t xml:space="preserve">Closing per Ledger 23-Mar-26 (Dr +/Cr -)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB less Ledger (must be nil)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Capital Account / Partners Capital</t>
   </si>
   <si>
@@ -232,15 +238,18 @@
     <t xml:space="preserve">Loan - Manasa</t>
   </si>
   <si>
+    <t xml:space="preserve">Short-term borrowings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samartha  Raghava NAgabhushanam-Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan - Samartha Raghava Nagabhushanam</t>
+  </si>
+  <si>
     <t xml:space="preserve">Long-term borrowings</t>
   </si>
   <si>
-    <t xml:space="preserve">Samartha  Raghava NAgabhushanam-Loan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan - Samartha Raghava Nagabhushanam</t>
-  </si>
-  <si>
     <t xml:space="preserve">194 J-TDS on Profession</t>
   </si>
   <si>
@@ -532,6 +541,9 @@
     <t xml:space="preserve">Difference: mapped total less Tally Grand Total (must be nil)</t>
   </si>
   <si>
+    <t xml:space="preserve">Total TB less Ledger -&gt;</t>
+  </si>
+  <si>
     <t xml:space="preserve">Difference: Debit less Credit (must be nil)</t>
   </si>
   <si>
@@ -580,18 +592,24 @@
     <t xml:space="preserve">Current Liabilities</t>
   </si>
   <si>
-    <t xml:space="preserve">(a) Trade payables</t>
+    <t xml:space="preserve">(a) Short-term borrowings</t>
   </si>
   <si>
     <t xml:space="preserve">2.4</t>
   </si>
   <si>
-    <t xml:space="preserve">(b) Other current liabilities</t>
+    <t xml:space="preserve">(b) Trade payables</t>
   </si>
   <si>
     <t xml:space="preserve">2.5</t>
   </si>
   <si>
+    <t xml:space="preserve">(c) Other current liabilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Current Liabilities</t>
   </si>
   <si>
@@ -616,19 +634,19 @@
     <t xml:space="preserve">(a) Cash and cash equivalents</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6</t>
+    <t xml:space="preserve">2.7</t>
   </si>
   <si>
     <t xml:space="preserve">(b) Short-term loans and advances</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7</t>
+    <t xml:space="preserve">2.8</t>
   </si>
   <si>
     <t xml:space="preserve">(c) Other current assets</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8</t>
+    <t xml:space="preserve">2.9</t>
   </si>
   <si>
     <t xml:space="preserve">SIGNIFICANT ACCOUNTING POLICIES,
@@ -653,7 +671,7 @@
     <t xml:space="preserve">(a) Revenue from operations</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9</t>
+    <t xml:space="preserve">2.10</t>
   </si>
   <si>
     <t xml:space="preserve">(b) Other income</t>
@@ -668,7 +686,7 @@
     <t xml:space="preserve">(A) Other expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10</t>
+    <t xml:space="preserve">2.11</t>
   </si>
   <si>
     <t xml:space="preserve">Total Expenses</t>
@@ -767,7 +785,10 @@
     <t xml:space="preserve">Unsecured loans</t>
   </si>
   <si>
-    <t xml:space="preserve">From others - Manasa</t>
+    <t xml:space="preserve">Unsecured loans, repayable on demand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From others - Manasa (amounts advanced and expenses incurred on behalf of the LLP)</t>
   </si>
   <si>
     <t xml:space="preserve">Outstanding dues of;</t>
@@ -812,6 +833,9 @@
     <t xml:space="preserve">Input SGST 9%</t>
   </si>
   <si>
+    <t xml:space="preserve">B2C Sales (online, collected through payment gateway)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Accommodation and Hotel Expenses</t>
   </si>
   <si>
@@ -845,7 +869,7 @@
     <t xml:space="preserve">Website Development Expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11  Related Party Disclosures</t>
+    <t xml:space="preserve">2.12  Related Party Disclosures</t>
   </si>
   <si>
     <t xml:space="preserve">a. Designated Partners / Key Management Personnel:</t>
@@ -878,13 +902,16 @@
     <t xml:space="preserve">Unsecured loan from partner (closing balance)</t>
   </si>
   <si>
-    <t xml:space="preserve">Unsecured loan from partner - net amount received during the year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No interest on the loan from the partner and no remuneration to partners has been charged in the books for the year (previous year: Nil). The previous-year figure of net loan received is stated on the basis that no opening balances appear in the Trial Balance for 2024-25.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12 - Previous period figures</t>
+    <t xml:space="preserve">Unsecured loan received from partner during the year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsecured loan repaid to partner during the year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The loan from the partner was received in nine tranches through the bank account during the year and no amount was repaid (per ledger). No interest on the loan and no remuneration to partners has been charged in the books for the year (previous year: Nil). The previous-year figure of loan received is stated on the basis that no opening balances appear in the Trial Balance for 2024-25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13 - Previous period figures</t>
   </si>
   <si>
     <t xml:space="preserve">Previous year's figures have been regrouped / reclassified wherever necessary to conform to the current year's presentation.</t>
@@ -905,16 +932,64 @@
     <t xml:space="preserve">Information required / treatment adopted</t>
   </si>
   <si>
-    <t xml:space="preserve">The FY 2025-26 Trial Balance exported from Tally covers 1-Apr-25 to 23-Mar-26, not the full year to 31-Mar-26.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statements are presented as at March 31, 2026 (FY 2025-26) as instructed. Transactions from 24-Mar-26 to 31-Mar-26 (if any) are not included. A TB to 31-Mar-26 should be re-exported and pasted into the TB sheet.</t>
+    <t xml:space="preserve">Period / cut-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The FY 2025-26 Trial Balance and ledgers run from 1-Apr-25 to 23-Mar-26. Sales are booked by one summary Sales voucher per month and the last one is dated 28-Feb-26; the last Razorpay settlement received in the bank is dated 27-Feb-26; there are no sales in April 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statements are presented as at March 31, 2026 (FY 2025-26) as instructed, on the books as they stand. Revenue and Razorpay settlements for March 2026 (and 24 to 31 March bank transactions) are not yet recorded. Book the March sales voucher and settlements, re-export the TB to 31-Mar-26 and paste it into the TB sheet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank - credit balance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per the Kotak ledger (446 entries) the book balance stays positive all year and turns to a credit of Rs 2,593.05 only on the last entry (15-Mar-26, payment of Rs 5,000 to Yuvaraj). March Razorpay settlements are unrecorded (see item 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presented as "Book overdraft" under Other current liabilities (Note 2.6) since a credit bank balance cannot be shown as cash. It is a book overdraft from unrecorded receipts, not a bank overdraft, and should reverse once March receipts are booked. Confirm against the bank statement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Cash" ledger is not physical cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 22 entries in the Cash ledger are monthly Sales (Dr) and monthly transfers to the Razorpay ledger (Cr). The closing Rs 20,754.20 is the cumulative difference between sales booked (Rs 12,50,048.98 incl. GST) and amounts transferred to Razorpay (Rs 12,29,294.78). Separately the Razorpay ledger has a CREDIT balance of Rs 30,452.56 (settlements + commission exceed collections booked) which sits inside Sundry Creditors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both balances are presented exactly as per the TB (Cash in hand, Note 2.7; Razorpay within Trade payables, Note 2.5) because they are unreconciled. Reconcile with the Razorpay settlement statement; the net position (Rs 9,698.36 payable) should then be reclassified as a receivable/payable from the payment gateway, not cash.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manasa - reclassified to Short-term borrowings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tally groups Manasa under Unsecured Loans. The ledger shows a running account: Rs 80,000 received (12-Feb-26), Rs 1,52,180 of LLP expenses paid personally by Manasa (Facebook ads 60,000; travel 63,218; pooja 10,000; Vinyas Kumar 9,000; Halaswamy 5,600; Bhadri Narayan 3,500; conveyance 862) and Rs 62,000 repaid in six tranches within the year. Closing Rs 1,70,180.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Because the balance is settled on demand within the year, it is presented under Short-term borrowings (Note 2.4) rather than Long-term borrowings. This is the only classification that differs from the Tally group; revert by changing the Head in the TB sheet if not agreed. Confirm Manasa's relationship to the partners (pays LLP expenses from personal funds; possibly a related party).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partner loan - resolved from ledger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan from Samartha Raghava Nagabhushanam: opening Rs 7,80,680; received Rs 17,00,000 in nine bank tranches (6-Apr-25 to 19-Feb-26); nothing repaid; closing Rs 24,80,680. One tranche (16-Oct-25, Rs 1,00,000) is entered with voucher type "Payment" although the bank was debited; several Razorpay/Facebook entries also carry inverted voucher types.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross receipts and repayments are now disclosed in Note 2.12 (items 3 and 4). Amounts are unaffected by the voucher-type inconsistencies but the voucher types should be corrected in Tally. Tenure and interest terms are still not in the books; kept under Long-term borrowings following the reference mapping (Directors Loan -&gt; Long-term borrowings). No interest has been charged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probable related party - Nayana Nagabhushanam (Drishti Commn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design and Development services of Rs 60,000 (3 x Rs 20,000; TDS Rs 6,000; Rs 54,000 paid) were availed from Nayana Nagabhushanam, who shares the partner's surname. Fully settled; nil closing balance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not disclosed as a related party because the relationship is not evidenced in the books. If Nayana Nagabhushanam is a relative of the partner, add "Availing of services - Rs 60,000" to Note 2.12.</t>
   </si>
   <si>
     <t xml:space="preserve">Entity / partners</t>
   </si>
   <si>
-    <t xml:space="preserve">Only one partner capital account appears in the TB (Samartha R .N - Captial Account, Rs 90,000). An LLP must have at least two partners.</t>
+    <t xml:space="preserve">Only one partner capital account appears in the books (Samartha R .N - Captial Account, Rs 90,000, no movement in either year). An LLP must have at least two partners.</t>
   </si>
   <si>
     <t xml:space="preserve">Second designated partner name, DPIN, capital (if any) and profit-sharing ratio are required. Placeholders are in the Master sheet (yellow cells). Note 2.1(D) currently shows 100% contribution by the one partner in the TB.</t>
@@ -923,130 +998,100 @@
     <t xml:space="preserve">Entity details</t>
   </si>
   <si>
-    <t xml:space="preserve">LLPIN, PAN, LLP Agreement terms, incorporation date, auditor name/firm/FRN/membership no./UDIN, signing dates and places are not available in the TB.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill the yellow cells in the Master sheet; all headers and signature blocks are linked to them. Note: statutory audit of an LLP is mandatory only if turnover exceeds Rs 40 lakh or contribution exceeds Rs 25 lakh; neither threshold is met per the TB, so confirm whether an auditor block is required.</t>
+    <t xml:space="preserve">LLPIN, PAN, LLP Agreement terms, incorporation date, auditor name/firm/FRN/membership no./UDIN, signing dates and places are not in the books.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fill the yellow cells in the Master sheet; all headers and signature blocks are linked to them. Statutory audit of an LLP is mandatory only if turnover exceeds Rs 40 lakh or contribution exceeds Rs 25 lakh; neither threshold is met, so confirm whether an auditor block is required.</t>
   </si>
   <si>
     <t xml:space="preserve">Format</t>
   </si>
   <si>
-    <t xml:space="preserve">The reference (Checkaro) is a Private Limited Company under Schedule III. The entity here is an LLP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Layout, fonts, rounding and note structure follow the reference exactly. Captions have been changed only where the entity type dictates: Share capital -&gt; Partners' capital; Shareholder's funds -&gt; Partners' funds; Board of Directors/Director/DIN -&gt; Partners/Designated Partner/DPIN. Earnings per share and promoter shareholding (not applicable to an LLP) are omitted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kotak Mahindra Bank ledger has a CREDIT balance of Rs 2,593.05 at 23-Mar-26 (Dr 12,768.48 at 31-Mar-25).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A credit bank balance cannot be shown as cash. Presented as "Book overdraft - Kotak Mahindra Bank" under Other current liabilities (Note 2.5). Confirm against bank statement / BRS whether this is an actual overdraft or unrecorded receipts / timing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sundry creditors - debit balances</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Five Sundry Creditor ledgers have DEBIT balances totalling Rs 1,73,500 (Mangala 15,000; Sriguru P V 20,000; Subodh Kumar Mishra 1,21,000; Swami Gangaram 2,500; Yuvaraj 15,000).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presented as advances to suppliers/consultants under Short-term loans and advances (Note 2.7), not netted against payables. Confirm they are genuine advances and not unrecorded bills or payments posted to wrong ledgers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loans (Liability): Samartha Raghava Nagabhushanam Rs 24,80,680 (PY 7,80,680) and Manasa Rs 1,70,180 (PY Nil). No repayment terms, interest or tenure in the TB.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Classified as Long-term borrowings (Note 2.3), following the reference mapping of Directors Loan -&gt; Long-term borrowings. Confirm tenure (if repayable within 12 months they belong under Short-term borrowings), interest (none charged in TB) and the relationship of Manasa (related party?).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Related parties</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partner Samartha Raghava Nagabhushanam: capital Rs 90,000; loan closing Rs 24,80,680; net loan received during FY 25-26 Rs 17,00,000 (closing less PY closing). Many creditors are individuals grouped as "Consultants".</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Only the partner is disclosed as related party (Note 2.11). Gross loan receipts/repayments are not determinable from a TB (only net movement). Confirm whether any consultant/creditor (e.g. Madhavi K Rs 90,000, Sathyanarayana Bhat Rs 64,590) or lender Manasa is a relative of a partner.</t>
+    <t xml:space="preserve">The reference (Checkaro) is a Private Limited Company under Schedule III. This entity is an LLP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Layout, fonts, rounding and note structure follow the reference. Captions changed only where the entity type dictates: Share capital -&gt; Partners' capital; Shareholder's funds -&gt; Partners' funds; Board of Directors/Director/DIN -&gt; Partners/Designated Partner/DPIN. Earnings per share and promoter shareholding are omitted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advances (debit balances in Sundry Creditors) - detail from ledgers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subodh Kumar Mishra: pooja bills Rs 1,26,000 vs paid Rs 2,47,000 -&gt; Rs 1,21,000 advance. Yuvaraj: professional bill Rs 27,000 (net of TDS) vs paid Rs 42,000 -&gt; Rs 15,000. Mangala Rs 15,000 (21-Jan-26), Sriguru P V Rs 20,000 (14-Feb-26) and Swami Gangaram Rs 2,500 (14-Jan-26) are single bank payments with no bill recorded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presented as advances to suppliers/consultants under Short-term loans and advances (Note 2.8), not netted against payables. If these payments were for services already rendered (pooja/professional fees), the bills should be booked, which would increase expenses by up to Rs 1,73,500 and reduce the advances.</t>
   </si>
   <si>
     <t xml:space="preserve">Trade payables - MSME</t>
   </si>
   <si>
-    <t xml:space="preserve">Sundry Creditors (credit balances) Rs 5,48,320.48 (PY 2,28,000). MSME status of suppliers is not in the TB.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entire amount shown under "other than micro and small enterprises" pending MSME confirmation (Note 2.4). Schedule III ageing schedule is not prepared: due-date information is not in a TB (and Schedule III does not apply to an LLP).</t>
+    <t xml:space="preserve">Sundry Creditors (credit balances) Rs 5,48,320.48 (PY 2,28,000), mostly individual consultants and pooja performers, plus Facebook India Rs 1,63,951.21, Razorpay Rs 30,452.56, Bharti Airtel, Google. MSME status is not in the books.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entire amount shown under "other than micro and small enterprises" pending MSME confirmation (Note 2.5). Schedule III ageing is not prepared (due dates not in the books; Schedule III does not apply to an LLP).</t>
   </si>
   <si>
     <t xml:space="preserve">GST</t>
   </si>
   <si>
-    <t xml:space="preserve">GST Payable Rs 7,505.41 (credit) and Input CGST Rs 2,820.94 + Input SGST Rs 2,820.94 (debit) exist as separate ledgers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presented gross: GST payable under statutory dues (Note 2.5) and input credits under Other current assets (Note 2.8). Confirm with GSTR-3B / electronic credit ledger whether they should be set off and shown net.</t>
+    <t xml:space="preserve">GST Payable ledger: output GST Rs 1,90,685.44, set off against IGST input Rs 69,224.05 and CGST/SGST input Rs 14,662.98, paid Rs 99,293; closing payable Rs 7,505.41. Unutilised Input CGST Rs 2,820.94 and Input SGST Rs 2,820.94 remain as separate debit ledgers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presented gross: GST payable under statutory dues (Note 2.6) and input credits under Other current assets (Note 2.9). Confirm with GSTR-3B / electronic credit ledger whether they should be set off and shown net.</t>
   </si>
   <si>
     <t xml:space="preserve">Expense classification</t>
   </si>
   <si>
-    <t xml:space="preserve">All expenses are grouped by Tally under "Indirect Expenses". Pooja Expenses Rs 9,59,127.50 and Professional Charges Rs 10,08,252 together exceed revenue of Rs 10,59,363.54. Staff Welfare Rs 7,681 / Internship Charges Rs 12,000 are employee-related; Bank Charges Rs 880.63 could be finance cost.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All expenses are presented under a single "Other expenses" note (2.10) exactly as grouped in Tally, as in the reference. Confirm whether Pooja Expenses are direct cost of services and whether employee-benefit / finance-cost lines should be shown separately.</t>
+    <t xml:space="preserve">All expenses are grouped by Tally as Indirect Expenses. Pooja Expenses Rs 9,59,127.50 are payments to individual performers (Sathyanarayana Bhat 2,68,200; Ajay Pandey 1,55,000; Subodh Kumar Mishra 1,40,000; K Soorya 93,450; others). Professional Charges Rs 10,08,252 comprise ISBR 3,96,800; Madhavi K 2,56,452 (monthly retainer of Rs 45,000); Medha Sudarshan 1,00,000; Venkatesh, Sudhakar and Vinyas Kumar 75,000 each; Yuvaraj 30,000. Staff Welfare Rs 7,681 and Internship Charges Rs 12,000 (two stipends of Rs 6,000) are employee-related; Bank Charges Rs 880.63.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All expenses are presented under a single Other expenses note (2.11) exactly as grouped in Tally, as in the reference. Consider presenting Pooja Expenses as cost of services and employee-benefit / finance-cost lines separately if required.</t>
   </si>
   <si>
     <t xml:space="preserve">Pre-incorporation expenses</t>
   </si>
   <si>
-    <t xml:space="preserve">Pre-incorporation Expenses Rs 36,000 in FY 25-26 in addition to Rs 4,79,320 in FY 24-25.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Charged to P&amp;L as per TB. Confirm the nature of the FY 25-26 amount (second year after incorporation) and whether any amount should be treated differently.</t>
+    <t xml:space="preserve">Rs 36,000 charged on 6-Apr-25 by a single bank payment with no counterparty or narration, in addition to Rs 4,79,320 in FY 24-25.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Charged to P&amp;L as per books. Confirm the nature of this second-year payment.</t>
   </si>
   <si>
     <t xml:space="preserve">Statutory interest / fees</t>
   </si>
   <si>
-    <t xml:space="preserve">Interest on TDS Rs 2,164 (PY 780) and GST Late Filing Fees Rs 20 are charged to P&amp;L.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Presented as expenses per TB. These are typically disallowed for income-tax; no tax computation has been prepared (the reference tax working sheets were hidden, company-specific and broken with reference errors).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provisions not in TB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No audit fee provision, no depreciation/fixed assets, no income-tax provision, no interest on partner loan/capital, no partner remuneration appear in the TB.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nothing has been added. Current tax is Nil (loss year). If an audit fee or any year-end provision is to be booked, it must first be passed in Tally and the TB re-exported.</t>
+    <t xml:space="preserve">Interest on TDS Rs 2,164 (five payments, Jul to Oct 2025) and GST late filing fee Rs 20 are charged to P&amp;L.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presented as expenses per books. These are typically disallowed for income-tax; no tax computation has been prepared (the reference tax working sheets were hidden, company-specific and broken with reference errors).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provisions not in the books</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No audit fee provision, no depreciation/fixed assets, no income-tax provision, no interest on partner loan/capital, no partner remuneration appear in the books.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nothing has been added. Current tax is Nil (loss year). If an audit fee or any year-end provision is to be booked, pass it in Tally and re-export the TB.</t>
   </si>
   <si>
     <t xml:space="preserve">Going concern / net worth</t>
   </si>
   <si>
-    <t xml:space="preserve">Partners' funds are negative: Rs (30,31,142.86) at 23-Mar-26 (PY Rs (10,30,911.52)). Loss for the year Rs 20,00,231.34 on revenue Rs 10,59,363.54.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reported as per TB. Partners should confirm continued financial support (loans of Rs 26.5 lakh) for a going-concern statement in the accounting policies (Note 1), which is not part of the reference workbook and has not been prepared.</t>
+    <t xml:space="preserve">Partners' funds are negative: Rs (30,31,142.86) at 23-Mar-26 (PY Rs (10,30,911.52)). Loss for the year Rs 20,00,231.34 on revenue Rs 10,59,363.54. Operations are funded by the partner's loan of Rs 24.8 lakh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reported as per books. Partners should confirm continued financial support for a going-concern statement in the accounting policies (Note 1), which is not part of the reference workbook and has not been prepared.</t>
   </si>
   <si>
     <t xml:space="preserve">Rounding</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference presents amounts in Rs '00 (Master!B31 = 100) with display rounding, without ROUND() in formulas (same as reference).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Because underlying values carry paise, in Rs '00 the displayed components of TOTAL LIABILITIES (-30,311 + 26,509 + 5,802 = 2,000) differ by 1 from the displayed total (1,999); the underlying figures balance exactly. Set Master!B31 to 1 to present in full rupees, which removes this display difference.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cash in hand Rs 20,754.20 at 23-Mar-26 (PY Nil).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reported as per TB. Confirm physical cash count / cash book at year end.</t>
+    <t xml:space="preserve">Reference presents amounts in Rs '00 (Master!B31 = 100) with display rounding and no ROUND() in formulas (same as reference).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Because underlying values carry paise, in Rs '00 the displayed components of TOTAL LIABILITIES (-30,311 + 24,807 + 7,504 = 2,000) differ by 1 from the displayed total (1,999); the underlying figures balance exactly. Set Master!B31 to 1 to present in full rupees, which removes this display difference.</t>
   </si>
   <si>
     <t xml:space="preserve">Ledger names</t>
@@ -1055,25 +1100,34 @@
     <t xml:space="preserve">Several Tally ledger names contain spelling errors (e.g. "Telepohone Exenses", "Campaining", "Subscrptions", "Accomodation", "Captial").</t>
   </si>
   <si>
-    <t xml:space="preserve">Exact Tally names are retained in the TB sheet (column A and grouping keys). Only the presentation captions in Note 2.10 have corrected spelling; no amounts are affected.</t>
+    <t xml:space="preserve">Exact Tally names are retained in the TB sheet (column A and grouping keys). Only the presentation captions in Note 2.11 have corrected spelling; no amounts are affected.</t>
   </si>
   <si>
     <t xml:space="preserve">Previous year opening balances</t>
   </si>
   <si>
-    <t xml:space="preserve">The FY 24-25 TB has no brought-forward Profit &amp; Loss balance and includes Pre-incorporation Expenses, indicating FY 24-25 was the first year.</t>
+    <t xml:space="preserve">The FY 24-25 TB has no brought-forward Profit &amp; Loss balance and includes Pre-incorporation Expenses, indicating FY 24-25 was the first year. The FY 25-26 ledgers confirm the FY 24-25 closing balances as openings (capital 90,000; loan 7,80,680; TDS 35,000; creditors 2,28,000; bank 12,768.48; P&amp;L 11,20,911.52).</t>
   </si>
   <si>
     <t xml:space="preserve">PY opening capital (Note 2.1B) and PY opening reserves (Note 2.2) are therefore Nil and PY 'contributed / received during the year' equals the PY closing balance. Confirm the LLP's date of incorporation.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ledger tie-out (information)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 78 FY 2025-26 ledgers were re-cast: opening + debits - credits = closing for every ledger, and every closing balance agrees with the Trial Balance. Seven ledgers with nil closing balance (ISBR, Nayana Nagabhushanam, Dharani, Futura Digital, Halaswamy, Rakshith Adiga, Rishabh Marketing, Sreejit Nambiyar, Printo) do not appear in the TB.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB sheet columns K and L show the closing balance per ledger against each TB line and the difference (nil throughout). No amount in the statements differs from the books.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference sheets not carried</t>
   </si>
   <si>
     <t xml:space="preserve">Reference workbook contains hidden company income-tax working sheets (IT Depn, IT Comp, DTA, MAT, ARI) and a hidden trade-payables ageing sheet, all with reference errors and specific to a company.</t>
   </si>
   <si>
-    <t xml:space="preserve">Not reproduced (MAT, EPS, Schedule III ratios and ageing do not apply to an LLP; deferred tax not computed). Master and TB sheets are kept visible here so the mapping can be reviewed; hide them for printing if desired.</t>
+    <t xml:space="preserve">Not reproduced (MAT, EPS, Schedule III ratios and ageing do not apply to an LLP; deferred tax not computed). Master and TB sheets are kept visible so the mapping can be reviewed; hide them for printing if desired.</t>
   </si>
 </sst>
 </file>
@@ -1430,6 +1484,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1676,10 +1734,6 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2356,7 +2410,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:L79"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -2365,6 +2419,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2458,13 +2514,19 @@
       <c r="J6" s="24" t="s">
         <v>57</v>
       </c>
+      <c r="K6" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="24" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7" s="26"/>
       <c r="D7" s="26" t="n">
@@ -2483,18 +2545,25 @@
         <v>900</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>60</v>
+        <v>62</v>
+      </c>
+      <c r="K7" s="26" t="n">
+        <v>-90000</v>
+      </c>
+      <c r="L7" s="26" t="n">
+        <f aca="false">(C7-D7)-K7</f>
+        <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C8" s="26"/>
       <c r="D8" s="26" t="n">
@@ -2511,18 +2580,25 @@
         <v>0</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="J8" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>-170180</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <f aca="false">(C8-D8)-K8</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" s="26"/>
       <c r="D9" s="26" t="n">
@@ -2541,18 +2617,25 @@
         <v>7806.8</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J9" s="25" t="s">
-        <v>64</v>
+        <v>69</v>
+      </c>
+      <c r="K9" s="26" t="n">
+        <v>-2480680</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <f aca="false">(C9-D9)-K9</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C10" s="26"/>
       <c r="D10" s="26" t="n">
@@ -2571,18 +2654,25 @@
         <v>350</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J10" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>-21760</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <f aca="false">(C10-D10)-K10</f>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>71</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>68</v>
       </c>
       <c r="C11" s="26"/>
       <c r="D11" s="26" t="n">
@@ -2599,18 +2689,25 @@
         <v>0</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J11" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="K11" s="26" t="n">
+        <v>-7505.41</v>
+      </c>
+      <c r="L11" s="26" t="n">
+        <f aca="false">(C11-D11)-K11</f>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C12" s="26" t="n">
         <v>2820.94</v>
@@ -2627,18 +2724,25 @@
         <v>0</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>2820.94</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <f aca="false">(C12-D12)-K12</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C13" s="26" t="n">
         <v>2820.94</v>
@@ -2655,18 +2759,25 @@
         <v>0</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J13" s="25" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="K13" s="26" t="n">
+        <v>2820.94</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <f aca="false">(C13-D13)-K13</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C14" s="26"/>
       <c r="D14" s="26" t="n">
@@ -2683,18 +2794,25 @@
         <v>0</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J14" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>-30800</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <f aca="false">(C14-D14)-K14</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="25" t="s">
         <v>81</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>78</v>
       </c>
       <c r="C15" s="26"/>
       <c r="D15" s="26" t="n">
@@ -2711,18 +2829,25 @@
         <v>0</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>-8606.5</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <f aca="false">(C15-D15)-K15</f>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C16" s="26"/>
       <c r="D16" s="26" t="n">
@@ -2739,18 +2864,25 @@
         <v>0</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J16" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>-6339.78</v>
+      </c>
+      <c r="L16" s="26" t="n">
+        <f aca="false">(C16-D16)-K16</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C17" s="26"/>
       <c r="D17" s="26" t="n">
@@ -2767,18 +2899,25 @@
         <v>0</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J17" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>-3000</v>
+      </c>
+      <c r="L17" s="26" t="n">
+        <f aca="false">(C17-D17)-K17</f>
+        <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C18" s="26"/>
       <c r="D18" s="26" t="n">
@@ -2795,18 +2934,25 @@
         <v>0</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J18" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>-8815</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <f aca="false">(C18-D18)-K18</f>
+        <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C19" s="26"/>
       <c r="D19" s="26" t="n">
@@ -2823,18 +2969,25 @@
         <v>0</v>
       </c>
       <c r="I19" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J19" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>-163951.21</v>
+      </c>
+      <c r="L19" s="26" t="n">
+        <f aca="false">(C19-D19)-K19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C20" s="26"/>
       <c r="D20" s="26" t="n">
@@ -2851,18 +3004,25 @@
         <v>0</v>
       </c>
       <c r="I20" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J20" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>-3657.53</v>
+      </c>
+      <c r="L20" s="26" t="n">
+        <f aca="false">(C20-D20)-K20</f>
+        <v>0</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" s="26"/>
       <c r="D21" s="26" t="n">
@@ -2879,18 +3039,25 @@
         <v>0</v>
       </c>
       <c r="I21" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J21" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K21" s="26" t="n">
+        <v>-9263</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <f aca="false">(C21-D21)-K21</f>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C22" s="26"/>
       <c r="D22" s="26" t="n">
@@ -2907,18 +3074,25 @@
         <v>0</v>
       </c>
       <c r="I22" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J22" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K22" s="26" t="n">
+        <v>-5400</v>
+      </c>
+      <c r="L22" s="26" t="n">
+        <f aca="false">(C22-D22)-K22</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C23" s="26"/>
       <c r="D23" s="26" t="n">
@@ -2935,18 +3109,25 @@
         <v>0</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J23" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K23" s="26" t="n">
+        <v>-33930</v>
+      </c>
+      <c r="L23" s="26" t="n">
+        <f aca="false">(C23-D23)-K23</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C24" s="26"/>
       <c r="D24" s="26" t="n">
@@ -2963,18 +3144,25 @@
         <v>0</v>
       </c>
       <c r="I24" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J24" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K24" s="26" t="n">
+        <v>-90000</v>
+      </c>
+      <c r="L24" s="26" t="n">
+        <f aca="false">(C24-D24)-K24</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C25" s="26"/>
       <c r="D25" s="26" t="n">
@@ -2991,18 +3179,25 @@
         <v>0</v>
       </c>
       <c r="I25" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J25" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K25" s="26" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <f aca="false">(C25-D25)-K25</f>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C26" s="26"/>
       <c r="D26" s="26" t="n">
@@ -3019,18 +3214,25 @@
         <v>0</v>
       </c>
       <c r="I26" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J26" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K26" s="26" t="n">
+        <v>-2000.9</v>
+      </c>
+      <c r="L26" s="26" t="n">
+        <f aca="false">(C26-D26)-K26</f>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C27" s="26"/>
       <c r="D27" s="26" t="n">
@@ -3047,18 +3249,25 @@
         <v>0</v>
       </c>
       <c r="I27" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J27" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K27" s="26" t="n">
+        <v>-30452.56</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <f aca="false">(C27-D27)-K27</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C28" s="26"/>
       <c r="D28" s="26" t="n">
@@ -3075,18 +3284,25 @@
         <v>0</v>
       </c>
       <c r="I28" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J28" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K28" s="26" t="n">
+        <v>-64590</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <f aca="false">(C28-D28)-K28</f>
+        <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C29" s="26"/>
       <c r="D29" s="26" t="n">
@@ -3103,18 +3319,25 @@
         <v>0</v>
       </c>
       <c r="I29" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J29" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K29" s="26" t="n">
+        <v>-520</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <f aca="false">(C29-D29)-K29</f>
+        <v>0</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B30" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C30" s="26"/>
       <c r="D30" s="26" t="n">
@@ -3131,18 +3354,25 @@
         <v>0</v>
       </c>
       <c r="I30" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J30" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K30" s="26" t="n">
+        <v>-2484</v>
+      </c>
+      <c r="L30" s="26" t="n">
+        <f aca="false">(C30-D30)-K30</f>
+        <v>0</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C31" s="26"/>
       <c r="D31" s="26" t="n">
@@ -3159,18 +3389,25 @@
         <v>0</v>
       </c>
       <c r="I31" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J31" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K31" s="26" t="n">
+        <v>-21500</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <f aca="false">(C31-D31)-K31</f>
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B32" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C32" s="26"/>
       <c r="D32" s="26" t="n">
@@ -3187,18 +3424,25 @@
         <v>0</v>
       </c>
       <c r="I32" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J32" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K32" s="26" t="n">
+        <v>-22500</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <f aca="false">(C32-D32)-K32</f>
+        <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B33" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C33" s="26"/>
       <c r="D33" s="26" t="n">
@@ -3217,18 +3461,25 @@
         <v>675</v>
       </c>
       <c r="I33" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J33" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K33" s="26" t="n">
+        <v>-16528</v>
+      </c>
+      <c r="L33" s="26" t="n">
+        <f aca="false">(C33-D33)-K33</f>
+        <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B34" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="26" t="n">
@@ -3245,18 +3496,25 @@
         <v>0</v>
       </c>
       <c r="I34" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J34" s="25" t="s">
-        <v>80</v>
+        <v>83</v>
+      </c>
+      <c r="K34" s="26" t="n">
+        <v>-18982</v>
+      </c>
+      <c r="L34" s="26" t="n">
+        <f aca="false">(C34-D34)-K34</f>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B35" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="26"/>
@@ -3273,18 +3531,20 @@
         <v>30</v>
       </c>
       <c r="I35" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J35" s="25" t="s">
-        <v>80</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B36" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C36" s="26"/>
       <c r="D36" s="26"/>
@@ -3301,18 +3561,20 @@
         <v>900</v>
       </c>
       <c r="I36" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J36" s="25" t="s">
-        <v>80</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B37" s="25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C37" s="26"/>
       <c r="D37" s="26"/>
@@ -3329,18 +3591,20 @@
         <v>675</v>
       </c>
       <c r="I37" s="25" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J37" s="25" t="s">
-        <v>80</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B38" s="25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C38" s="26" t="n">
         <v>15000</v>
@@ -3357,18 +3621,25 @@
         <v>0</v>
       </c>
       <c r="I38" s="25" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J38" s="25" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="K38" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L38" s="26" t="n">
+        <f aca="false">(C38-D38)-K38</f>
+        <v>0</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" s="25" t="s">
         <v>108</v>
-      </c>
-      <c r="B39" s="25" t="s">
-        <v>105</v>
       </c>
       <c r="C39" s="26" t="n">
         <v>20000</v>
@@ -3385,18 +3656,25 @@
         <v>0</v>
       </c>
       <c r="I39" s="25" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J39" s="25" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="K39" s="26" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L39" s="26" t="n">
+        <f aca="false">(C39-D39)-K39</f>
+        <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B40" s="25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C40" s="26" t="n">
         <v>121000</v>
@@ -3413,18 +3691,25 @@
         <v>0</v>
       </c>
       <c r="I40" s="25" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J40" s="25" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="K40" s="26" t="n">
+        <v>121000</v>
+      </c>
+      <c r="L40" s="26" t="n">
+        <f aca="false">(C40-D40)-K40</f>
+        <v>0</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B41" s="25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C41" s="26" t="n">
         <v>2500</v>
@@ -3441,18 +3726,25 @@
         <v>0</v>
       </c>
       <c r="I41" s="25" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J41" s="25" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="K41" s="26" t="n">
+        <v>2500</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <f aca="false">(C41-D41)-K41</f>
+        <v>0</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C42" s="26" t="n">
         <v>15000</v>
@@ -3469,18 +3761,25 @@
         <v>0</v>
       </c>
       <c r="I42" s="25" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J42" s="25" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="K42" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L42" s="26" t="n">
+        <f aca="false">(C42-D42)-K42</f>
+        <v>0</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B43" s="25" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C43" s="26" t="n">
         <v>20754.2</v>
@@ -3497,18 +3796,25 @@
         <v>0</v>
       </c>
       <c r="I43" s="25" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="J43" s="25" t="s">
-        <v>119</v>
+        <v>122</v>
+      </c>
+      <c r="K43" s="26" t="n">
+        <v>20754.2</v>
+      </c>
+      <c r="L43" s="26" t="n">
+        <f aca="false">(C43-D43)-K43</f>
+        <v>0</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C44" s="26"/>
       <c r="D44" s="26"/>
@@ -3525,18 +3831,20 @@
         <v>127.6848</v>
       </c>
       <c r="I44" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="J44" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="J44" s="25" t="s">
-        <v>119</v>
-      </c>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B45" s="25" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C45" s="26"/>
       <c r="D45" s="26" t="n">
@@ -3553,18 +3861,25 @@
         <v>0</v>
       </c>
       <c r="I45" s="25" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J45" s="25" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="K45" s="26" t="n">
+        <v>-2593.05</v>
+      </c>
+      <c r="L45" s="26" t="n">
+        <f aca="false">(C45-D45)-K45</f>
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C46" s="26"/>
       <c r="D46" s="26" t="n">
@@ -3581,18 +3896,25 @@
         <v>0</v>
       </c>
       <c r="I46" s="25" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>127</v>
+        <v>130</v>
+      </c>
+      <c r="K46" s="26" t="n">
+        <v>-1059363.54</v>
+      </c>
+      <c r="L46" s="26" t="n">
+        <f aca="false">(C46-D46)-K46</f>
+        <v>0</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B47" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C47" s="26" t="n">
         <v>17510</v>
@@ -3609,18 +3931,25 @@
         <v>0</v>
       </c>
       <c r="I47" s="25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K47" s="26" t="n">
+        <v>17510</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <f aca="false">(C47-D47)-K47</f>
+        <v>0</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B48" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C48" s="26" t="n">
         <v>410685.35</v>
@@ -3637,18 +3966,25 @@
         <v>0</v>
       </c>
       <c r="I48" s="25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J48" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K48" s="26" t="n">
+        <v>410685.35</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <f aca="false">(C48-D48)-K48</f>
+        <v>0</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B49" s="25" t="s">
         <v>132</v>
-      </c>
-      <c r="B49" s="25" t="s">
-        <v>129</v>
       </c>
       <c r="C49" s="26" t="n">
         <v>880.63</v>
@@ -3667,18 +4003,25 @@
         <v>3.1152</v>
       </c>
       <c r="I49" s="25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J49" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K49" s="26" t="n">
+        <v>880.63</v>
+      </c>
+      <c r="L49" s="26" t="n">
+        <f aca="false">(C49-D49)-K49</f>
+        <v>0</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C50" s="26" t="n">
         <v>19100</v>
@@ -3695,18 +4038,25 @@
         <v>0</v>
       </c>
       <c r="I50" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="J50" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="J50" s="25" t="s">
-        <v>130</v>
+      <c r="K50" s="26" t="n">
+        <v>19100</v>
+      </c>
+      <c r="L50" s="26" t="n">
+        <f aca="false">(C50-D50)-K50</f>
+        <v>0</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C51" s="26" t="n">
         <v>25373</v>
@@ -3723,18 +4073,25 @@
         <v>0</v>
       </c>
       <c r="I51" s="25" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="J51" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K51" s="26" t="n">
+        <v>25373</v>
+      </c>
+      <c r="L51" s="26" t="n">
+        <f aca="false">(C51-D51)-K51</f>
+        <v>0</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C52" s="26" t="n">
         <v>26223.64</v>
@@ -3751,18 +4108,25 @@
         <v>0</v>
       </c>
       <c r="I52" s="25" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J52" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K52" s="26" t="n">
+        <v>26223.64</v>
+      </c>
+      <c r="L52" s="26" t="n">
+        <f aca="false">(C52-D52)-K52</f>
+        <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C53" s="26" t="n">
         <v>70000</v>
@@ -3779,18 +4143,25 @@
         <v>0</v>
       </c>
       <c r="I53" s="25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K53" s="26" t="n">
+        <v>70000</v>
+      </c>
+      <c r="L53" s="26" t="n">
+        <f aca="false">(C53-D53)-K53</f>
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
@@ -3807,18 +4178,20 @@
         <v>25</v>
       </c>
       <c r="I54" s="25" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="J54" s="25" t="s">
-        <v>130</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C55" s="26" t="n">
         <v>20</v>
@@ -3835,18 +4208,25 @@
         <v>0</v>
       </c>
       <c r="I55" s="25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J55" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K55" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="L55" s="26" t="n">
+        <f aca="false">(C55-D55)-K55</f>
+        <v>0</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C56" s="26" t="n">
         <v>2164</v>
@@ -3865,18 +4245,25 @@
         <v>7.8</v>
       </c>
       <c r="I56" s="25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K56" s="26" t="n">
+        <v>2164</v>
+      </c>
+      <c r="L56" s="26" t="n">
+        <f aca="false">(C56-D56)-K56</f>
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C57" s="26" t="n">
         <v>12000</v>
@@ -3893,18 +4280,25 @@
         <v>0</v>
       </c>
       <c r="I57" s="25" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K57" s="26" t="n">
+        <v>12000</v>
+      </c>
+      <c r="L57" s="26" t="n">
+        <f aca="false">(C57-D57)-K57</f>
+        <v>0</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B58" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C58" s="26" t="n">
         <v>177417</v>
@@ -3921,18 +4315,25 @@
         <v>0</v>
       </c>
       <c r="I58" s="25" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K58" s="26" t="n">
+        <v>177417</v>
+      </c>
+      <c r="L58" s="26" t="n">
+        <f aca="false">(C58-D58)-K58</f>
+        <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C59" s="26" t="n">
         <v>9871.95</v>
@@ -3949,18 +4350,25 @@
         <v>0</v>
       </c>
       <c r="I59" s="25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K59" s="26" t="n">
+        <v>9871.95</v>
+      </c>
+      <c r="L59" s="26" t="n">
+        <f aca="false">(C59-D59)-K59</f>
+        <v>0</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C60" s="26" t="n">
         <v>80518</v>
@@ -3977,18 +4385,25 @@
         <v>0</v>
       </c>
       <c r="I60" s="25" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J60" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K60" s="26" t="n">
+        <v>80518</v>
+      </c>
+      <c r="L60" s="26" t="n">
+        <f aca="false">(C60-D60)-K60</f>
+        <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C61" s="26" t="n">
         <v>2535.68</v>
@@ -4005,18 +4420,25 @@
         <v>0</v>
       </c>
       <c r="I61" s="25" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="J61" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K61" s="26" t="n">
+        <v>2535.68</v>
+      </c>
+      <c r="L61" s="26" t="n">
+        <f aca="false">(C61-D61)-K61</f>
+        <v>0</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C62" s="26" t="n">
         <v>24901.09</v>
@@ -4033,18 +4455,25 @@
         <v>0</v>
       </c>
       <c r="I62" s="25" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J62" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K62" s="26" t="n">
+        <v>24901.09</v>
+      </c>
+      <c r="L62" s="26" t="n">
+        <f aca="false">(C62-D62)-K62</f>
+        <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C63" s="26" t="n">
         <v>959127.5</v>
@@ -4061,18 +4490,25 @@
         <v>0</v>
       </c>
       <c r="I63" s="25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J63" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K63" s="26" t="n">
+        <v>959127.5</v>
+      </c>
+      <c r="L63" s="26" t="n">
+        <f aca="false">(C63-D63)-K63</f>
+        <v>0</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C64" s="26" t="n">
         <v>24538</v>
@@ -4089,18 +4525,25 @@
         <v>0</v>
       </c>
       <c r="I64" s="25" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J64" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K64" s="26" t="n">
+        <v>24538</v>
+      </c>
+      <c r="L64" s="26" t="n">
+        <f aca="false">(C64-D64)-K64</f>
+        <v>0</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C65" s="26" t="n">
         <v>36000</v>
@@ -4119,18 +4562,25 @@
         <v>4793.2</v>
       </c>
       <c r="I65" s="25" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J65" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K65" s="26" t="n">
+        <v>36000</v>
+      </c>
+      <c r="L65" s="26" t="n">
+        <f aca="false">(C65-D65)-K65</f>
+        <v>0</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C66" s="26" t="n">
         <v>43036</v>
@@ -4147,18 +4597,25 @@
         <v>0</v>
       </c>
       <c r="I66" s="25" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="J66" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K66" s="26" t="n">
+        <v>43036</v>
+      </c>
+      <c r="L66" s="26" t="n">
+        <f aca="false">(C66-D66)-K66</f>
+        <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C67" s="26" t="n">
         <v>1008252</v>
@@ -4177,18 +4634,25 @@
         <v>4500</v>
       </c>
       <c r="I67" s="25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="J67" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K67" s="26" t="n">
+        <v>1008252</v>
+      </c>
+      <c r="L67" s="26" t="n">
+        <f aca="false">(C67-D67)-K67</f>
+        <v>0</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C68" s="26"/>
       <c r="D68" s="26"/>
@@ -4205,18 +4669,20 @@
         <v>350</v>
       </c>
       <c r="I68" s="25" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J68" s="25" t="s">
-        <v>130</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="K68" s="14"/>
+      <c r="L68" s="14"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C69" s="26" t="n">
         <v>0.04</v>
@@ -4233,18 +4699,25 @@
         <v>0</v>
       </c>
       <c r="I69" s="25" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="J69" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K69" s="26" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L69" s="26" t="n">
+        <f aca="false">(C69-D69)-K69</f>
+        <v>0</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C70" s="26" t="n">
         <v>7681</v>
@@ -4261,18 +4734,25 @@
         <v>0</v>
       </c>
       <c r="I70" s="25" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="J70" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K70" s="26" t="n">
+        <v>7681</v>
+      </c>
+      <c r="L70" s="26" t="n">
+        <f aca="false">(C70-D70)-K70</f>
+        <v>0</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C71" s="26" t="n">
         <v>24000</v>
@@ -4291,18 +4771,25 @@
         <v>280</v>
       </c>
       <c r="I71" s="25" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J71" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K71" s="26" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L71" s="26" t="n">
+        <f aca="false">(C71-D71)-K71</f>
+        <v>0</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C72" s="26" t="n">
         <v>15000</v>
@@ -4319,18 +4806,25 @@
         <v>0</v>
       </c>
       <c r="I72" s="25" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J72" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K72" s="26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L72" s="26" t="n">
+        <f aca="false">(C72-D72)-K72</f>
+        <v>0</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C73" s="26" t="n">
         <v>52760</v>
@@ -4347,18 +4841,25 @@
         <v>0</v>
       </c>
       <c r="I73" s="25" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J73" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K73" s="26" t="n">
+        <v>52760</v>
+      </c>
+      <c r="L73" s="26" t="n">
+        <f aca="false">(C73-D73)-K73</f>
+        <v>0</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C74" s="26" t="n">
         <v>10000</v>
@@ -4377,18 +4878,25 @@
         <v>1250</v>
       </c>
       <c r="I74" s="25" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J74" s="25" t="s">
-        <v>130</v>
+        <v>133</v>
+      </c>
+      <c r="K74" s="26" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L74" s="26" t="n">
+        <f aca="false">(C74-D74)-K74</f>
+        <v>0</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C75" s="26" t="n">
         <v>1120911.52</v>
@@ -4405,15 +4913,22 @@
         <v>0</v>
       </c>
       <c r="I75" s="25" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J75" s="25" t="s">
-        <v>161</v>
+        <v>164</v>
+      </c>
+      <c r="K75" s="26" t="n">
+        <v>1120911.52</v>
+      </c>
+      <c r="L75" s="26" t="n">
+        <f aca="false">(C75-D75)-K75</f>
+        <v>0</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="17" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C77" s="27" t="n">
         <v>4380402.48</v>
@@ -4430,7 +4945,7 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="17" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C78" s="20" t="n">
         <f aca="false">C4-C77</f>
@@ -4448,10 +4963,17 @@
         <f aca="false">F4-F77</f>
         <v>0</v>
       </c>
+      <c r="K78" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L78" s="20" t="n">
+        <f aca="false">SUM(L7:L75)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="17" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C79" s="20" t="n">
         <f aca="false">C4-D4</f>
@@ -4483,7 +5005,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -4507,7 +5029,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <f aca="false">Master!B3</f>
         <v>No 63, 1st Floor, 1st Main, 7th Block, Koramangala VI Block, Bangalore 560095</v>
       </c>
@@ -4525,433 +5047,449 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="D6" s="30" t="str">
+      <c r="A6" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="31" t="str">
         <f aca="false">Master!B33</f>
         <v>MARCH 31, 2026</v>
       </c>
-      <c r="E6" s="30" t="str">
+      <c r="E6" s="31" t="str">
         <f aca="false">Master!B34</f>
         <v>MARCH 31, 2025</v>
       </c>
-      <c r="G6" s="31" t="s">
-        <v>167</v>
+      <c r="G6" s="32" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="G7" s="35" t="str">
-        <f aca="false">"Total Liabilities less Total Assets (CY): "&amp;TEXT(D19-D31,"#,##0.00")</f>
+      <c r="A7" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="G7" s="36" t="str">
+        <f aca="false">"Total Liabilities less Total Assets (CY): "&amp;TEXT(D20-D32,"#,##0.00")</f>
         <v>Total Liabilities less Total Assets (CY): 0.00</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="G8" s="35" t="str">
-        <f aca="false">"Total Liabilities less Total Assets (PY): "&amp;TEXT(E19-E31,"#,##0.00")</f>
+      <c r="A8" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="G8" s="36" t="str">
+        <f aca="false">"Total Liabilities less Total Assets (PY): "&amp;TEXT(E20-E32,"#,##0.00")</f>
         <v>Total Liabilities less Total Assets (PY): 0.00</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="40" t="n">
+      <c r="A9" s="39" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="41" t="n">
         <f aca="false">'2.1'!D13</f>
         <v>900</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="41" t="n">
         <f aca="false">'2.1'!E13</f>
         <v>900</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="38" t="s">
-        <v>172</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!D15</f>
+      <c r="A10" s="39" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!D15</f>
         <v>-31211.4286</v>
       </c>
-      <c r="E10" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!E15</f>
+      <c r="E10" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!E15</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="41" t="s">
-        <v>174</v>
-      </c>
-      <c r="D11" s="42" t="n">
+      <c r="A11" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11" s="43" t="n">
         <f aca="false">SUM(D9:D10)</f>
         <v>-30311.4286</v>
       </c>
-      <c r="E11" s="42" t="n">
+      <c r="E11" s="43" t="n">
         <f aca="false">SUM(E9:E10)</f>
         <v>-10309.1152</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+      <c r="A12" s="37" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="43" t="n">
-        <f aca="false">'2.2 - 2.10'!D22</f>
-        <v>26508.6</v>
-      </c>
-      <c r="E13" s="43" t="n">
-        <f aca="false">'2.2 - 2.10'!E22</f>
+      <c r="A13" s="39" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>181</v>
+      </c>
+      <c r="D13" s="44" t="n">
+        <f aca="false">'2.2 - 2.11'!D21</f>
+        <v>24806.8</v>
+      </c>
+      <c r="E13" s="44" t="n">
+        <f aca="false">'2.2 - 2.11'!E21</f>
         <v>7806.8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="42" t="n">
+      <c r="A14" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="43" t="n">
         <f aca="false">SUM(D13:D13)</f>
-        <v>26508.6</v>
-      </c>
-      <c r="E14" s="42" t="n">
+        <v>24806.8</v>
+      </c>
+      <c r="E14" s="43" t="n">
         <f aca="false">SUM(E13:E13)</f>
         <v>7806.8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
+      <c r="A15" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
     </row>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="D16" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!D30</f>
+      <c r="A16" s="39" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="D16" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!D26</f>
+        <v>1701.8</v>
+      </c>
+      <c r="E16" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!E26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="C17" s="40" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!D34</f>
         <v>5483.2048</v>
       </c>
-      <c r="E16" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!E30</f>
+      <c r="E17" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!E34</f>
         <v>2280</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="D17" s="43" t="n">
-        <f aca="false">'2.2 - 2.10'!D39</f>
+    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>189</v>
+      </c>
+      <c r="D18" s="44" t="n">
+        <f aca="false">'2.2 - 2.11'!D43</f>
         <v>318.5846</v>
       </c>
-      <c r="E17" s="43" t="n">
-        <f aca="false">'2.2 - 2.10'!E39</f>
+      <c r="E18" s="44" t="n">
+        <f aca="false">'2.2 - 2.11'!E43</f>
         <v>350</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="D18" s="44" t="n">
-        <f aca="false">SUM(D16:D17)</f>
-        <v>5801.7894</v>
-      </c>
-      <c r="E18" s="44" t="n">
-        <f aca="false">SUM(E16:E17)</f>
+    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="D19" s="45" t="n">
+        <f aca="false">SUM(D16:D18)</f>
+        <v>7503.5894</v>
+      </c>
+      <c r="E19" s="45" t="n">
+        <f aca="false">SUM(E16:E18)</f>
         <v>2630</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="47" t="n">
-        <f aca="false">D11+D14+D18</f>
+    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="46" t="s">
+        <v>191</v>
+      </c>
+      <c r="B20" s="47"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="48" t="n">
+        <f aca="false">D11+D14+D19</f>
         <v>1998.9608</v>
       </c>
-      <c r="E19" s="47" t="n">
-        <f aca="false">E11+E14+E18</f>
+      <c r="E20" s="48" t="n">
+        <f aca="false">E11+E14+E19</f>
         <v>127.6848</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-    </row>
+    <row r="21" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
+      <c r="A22" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="38" t="s">
-        <v>188</v>
-      </c>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
+      <c r="A23" s="37" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="D24" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="40" t="n">
-        <v>0</v>
-      </c>
+      <c r="A24" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="41" t="str">
-        <f aca="false">"Total "&amp;A22</f>
+      <c r="A25" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="42" t="str">
+        <f aca="false">"Total "&amp;A23</f>
         <v>Total Non-current assets</v>
       </c>
-      <c r="D25" s="42" t="n">
-        <f aca="false">SUM(D24:D24)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="42" t="n">
-        <f aca="false">SUM(E24:E24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
+      <c r="D26" s="43" t="n">
+        <f aca="false">SUM(D25:D25)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="43" t="n">
+        <f aca="false">SUM(E25:E25)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>192</v>
-      </c>
-      <c r="D27" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!D45</f>
+      <c r="A27" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+    </row>
+    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!D49</f>
         <v>207.542</v>
       </c>
-      <c r="E27" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!E45</f>
+      <c r="E28" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!E49</f>
         <v>127.6848</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>194</v>
-      </c>
-      <c r="D28" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!D55</f>
+    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!D59</f>
         <v>1735</v>
       </c>
-      <c r="E28" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!E55</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>196</v>
-      </c>
-      <c r="D29" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!D62</f>
+      <c r="E29" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!E59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>202</v>
+      </c>
+      <c r="D30" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!D66</f>
         <v>56.4188</v>
       </c>
-      <c r="E29" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!E62</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="41" t="str">
-        <f aca="false">"Total "&amp;A26</f>
+      <c r="E30" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!E66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="42" t="str">
+        <f aca="false">"Total "&amp;A27</f>
         <v>Total Current assets</v>
       </c>
-      <c r="D30" s="44" t="n">
-        <f aca="false">SUM(D27:D29)</f>
+      <c r="D31" s="45" t="n">
+        <f aca="false">SUM(D28:D30)</f>
         <v>1998.9608</v>
       </c>
-      <c r="E30" s="44" t="n">
-        <f aca="false">SUM(E27:E29)</f>
+      <c r="E31" s="45" t="n">
+        <f aca="false">SUM(E28:E30)</f>
         <v>127.6848</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45" t="str">
-        <f aca="false">UPPER("Total "&amp;A21)</f>
+    <row r="32" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="46" t="str">
+        <f aca="false">UPPER("Total "&amp;A22)</f>
         <v>TOTAL ASSETS</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="48" t="n">
-        <f aca="false">D25+D30</f>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="49" t="n">
+        <f aca="false">D26+D31</f>
         <v>1998.9608</v>
       </c>
-      <c r="E31" s="48" t="n">
-        <f aca="false">E25+E30</f>
+      <c r="E32" s="49" t="n">
+        <f aca="false">E26+E31</f>
         <v>127.6848</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C33" s="50" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="B35" s="52" t="s">
-        <v>200</v>
+    <row r="33" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="18" t="str">
+      <c r="A36" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="B36" s="53" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="str">
         <f aca="false">"For "&amp;Master!B16</f>
         <v>For [To be provided]</v>
       </c>
-      <c r="B36" s="53" t="str">
+      <c r="B37" s="54" t="str">
         <f aca="false">Master!B2</f>
         <v>Daivbharathi Technologies LLP</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="54" t="str">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="55" t="str">
         <f aca="false">"(FRN: "&amp;Master!B17&amp;")"</f>
         <v>(FRN: [To be provided])</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="55" t="str">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="56" t="str">
         <f aca="false">UPPER(Master!B13)</f>
         <v>[TO BE PROVIDED]</v>
       </c>
-      <c r="B41" s="56" t="str">
+      <c r="B42" s="57" t="str">
         <f aca="false">UPPER(Master!B22)</f>
         <v>SAMARTHA RAGHAVA NAGABHUSHANAM</v>
       </c>
-      <c r="D41" s="56" t="str">
+      <c r="D42" s="57" t="str">
         <f aca="false">UPPER(Master!B26)</f>
         <v>[TO BE PROVIDED]</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="54" t="str">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="55" t="str">
         <f aca="false">PROPER(Master!B14)</f>
         <v>[To Be Provided]</v>
       </c>
-      <c r="B42" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D42" s="57" t="str">
-        <f aca="false">B42</f>
+      <c r="B43" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D43" s="58" t="str">
+        <f aca="false">B43</f>
         <v>Designated Partner</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="58" t="str">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="59" t="str">
         <f aca="false">"Membership No. "&amp;Master!B15</f>
         <v>Membership No. [To be provided]</v>
       </c>
-      <c r="B43" s="2" t="str">
+      <c r="B44" s="2" t="str">
         <f aca="false">"DPIN: "&amp;Master!B23</f>
         <v>DPIN: [To be provided]</v>
       </c>
-      <c r="D43" s="2" t="str">
+      <c r="D44" s="2" t="str">
         <f aca="false">"DPIN: "&amp;Master!B27</f>
         <v>DPIN: [To be provided]</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="58" t="str">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="59" t="str">
         <f aca="false">"UDIN: "&amp;Master!B18</f>
         <v>UDIN: [To be provided]</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="str">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="str">
         <f aca="false">Master!B19</f>
         <v>[To be provided]</v>
       </c>
-      <c r="B45" s="2" t="str">
+      <c r="B46" s="2" t="str">
         <f aca="false">Master!B24</f>
         <v>[To be provided]</v>
       </c>
-      <c r="D45" s="2" t="str">
+      <c r="D46" s="2" t="str">
         <f aca="false">Master!B28</f>
         <v>[To be provided]</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2" t="str">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="str">
         <f aca="false">Master!B20</f>
         <v>[To be provided]</v>
       </c>
-      <c r="B46" s="2" t="str">
+      <c r="B47" s="2" t="str">
         <f aca="false">Master!B25</f>
         <v>[To be provided]</v>
       </c>
-      <c r="D46" s="2" t="str">
+      <c r="D47" s="2" t="str">
         <f aca="false">Master!B29</f>
         <v>[To be provided]</v>
       </c>
@@ -4994,7 +5532,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <f aca="false">Master!B3</f>
         <v>No 63, 1st Floor, 1st Main, 7th Block, Koramangala VI Block, Bangalore 560095</v>
       </c>
@@ -5012,242 +5550,242 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="D6" s="30" t="str">
+      <c r="A6" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6" s="31" t="str">
         <f aca="false">Master!B33</f>
         <v>MARCH 31, 2026</v>
       </c>
-      <c r="E6" s="30" t="str">
+      <c r="E6" s="31" t="str">
         <f aca="false">Master!B34</f>
         <v>MARCH 31, 2025</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36" t="s">
-        <v>202</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+      <c r="A7" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
     </row>
     <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="D8" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!D68</f>
+      <c r="A8" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>210</v>
+      </c>
+      <c r="D8" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!D72</f>
         <v>10593.6354</v>
       </c>
-      <c r="E8" s="40" t="n">
-        <f aca="false">'2.2 - 2.10'!E68</f>
+      <c r="E8" s="41" t="n">
+        <f aca="false">'2.2 - 2.11'!E72</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="38" t="s">
-        <v>205</v>
-      </c>
-      <c r="D9" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="43" t="n">
+      <c r="A9" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="59" t="s">
-        <v>206</v>
-      </c>
-      <c r="D10" s="42" t="n">
+      <c r="A10" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="D10" s="43" t="n">
         <f aca="false">SUM(D8:D9)</f>
         <v>10593.6354</v>
       </c>
-      <c r="E10" s="42" t="n">
+      <c r="E10" s="43" t="n">
         <f aca="false">SUM(E8:E9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36" t="s">
-        <v>207</v>
-      </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
+      <c r="A12" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
     </row>
     <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="38" t="s">
-        <v>208</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>209</v>
-      </c>
-      <c r="D13" s="43" t="n">
-        <f aca="false">'2.2 - 2.10'!D105</f>
+      <c r="A13" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="44" t="n">
+        <f aca="false">'2.2 - 2.11'!D109</f>
         <v>30595.9488</v>
       </c>
-      <c r="E13" s="43" t="n">
-        <f aca="false">'2.2 - 2.10'!E105</f>
+      <c r="E13" s="44" t="n">
+        <f aca="false">'2.2 - 2.11'!E109</f>
         <v>11209.1152</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="59" t="s">
-        <v>210</v>
-      </c>
-      <c r="D14" s="42" t="n">
+      <c r="A14" s="60" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" s="43" t="n">
         <f aca="false">SUM(D13:D13)</f>
         <v>30595.9488</v>
       </c>
-      <c r="E14" s="42" t="n">
+      <c r="E14" s="43" t="n">
         <f aca="false">SUM(E13:E13)</f>
         <v>11209.1152</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="D16" s="42" t="n">
+      <c r="A16" s="37" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="43" t="n">
         <f aca="false">D10-D14</f>
         <v>-20002.3134</v>
       </c>
-      <c r="E16" s="42" t="n">
+      <c r="E16" s="43" t="n">
         <f aca="false">E10-E14</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="60" t="s">
-        <v>212</v>
-      </c>
-      <c r="D17" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="61" t="n">
+      <c r="A17" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="D18" s="42" t="n">
+      <c r="A18" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="D18" s="43" t="n">
         <f aca="false">D16-D17</f>
         <v>-20002.3134</v>
       </c>
-      <c r="E18" s="42" t="n">
+      <c r="E18" s="43" t="n">
         <f aca="false">E16-E17</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="60" t="s">
-        <v>214</v>
-      </c>
-      <c r="D19" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="61" t="n">
+      <c r="A19" s="61" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="62" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="D20" s="42" t="n">
+      <c r="A20" s="37" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="43" t="n">
         <f aca="false">D18+D19</f>
         <v>-20002.3134</v>
       </c>
-      <c r="E20" s="42" t="n">
+      <c r="E20" s="43" t="n">
         <f aca="false">E18+E19</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="36" t="s">
-        <v>216</v>
-      </c>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
+      <c r="A22" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
     </row>
     <row r="23" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="D23" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="40" t="n">
+      <c r="A23" s="42" t="s">
+        <v>223</v>
+      </c>
+      <c r="D23" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="41" t="s">
-        <v>218</v>
-      </c>
-      <c r="D24" s="43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="43" t="n">
+      <c r="A24" s="42" t="s">
+        <v>224</v>
+      </c>
+      <c r="D24" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="44" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="D25" s="42" t="n">
+      <c r="A25" s="60" t="s">
+        <v>225</v>
+      </c>
+      <c r="D25" s="43" t="n">
         <f aca="false">SUM(D23:D24)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="42" t="n">
+      <c r="E25" s="43" t="n">
         <f aca="false">SUM(E23:E24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="48" t="n">
+      <c r="A27" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="49" t="n">
         <f aca="false">D20-D25</f>
         <v>-20002.3134</v>
       </c>
-      <c r="E27" s="48" t="n">
+      <c r="E27" s="49" t="n">
         <f aca="false">E20-E25</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="29" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>198</v>
+      <c r="A29" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="B31" s="62" t="s">
-        <v>200</v>
+      <c r="A31" s="52" t="s">
+        <v>205</v>
+      </c>
+      <c r="B31" s="63" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5255,46 +5793,46 @@
         <f aca="false">"For "&amp;Master!B16</f>
         <v>For [To be provided]</v>
       </c>
-      <c r="B32" s="63" t="str">
+      <c r="B32" s="64" t="str">
         <f aca="false">Master!B2</f>
         <v>Daivbharathi Technologies LLP</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="54" t="str">
+      <c r="A33" s="55" t="str">
         <f aca="false">"(FRN: "&amp;Master!B17&amp;")"</f>
         <v>(FRN: [To be provided])</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="55" t="str">
+      <c r="A37" s="56" t="str">
         <f aca="false">UPPER(Master!B13)</f>
         <v>[TO BE PROVIDED]</v>
       </c>
-      <c r="B37" s="56" t="str">
+      <c r="B37" s="57" t="str">
         <f aca="false">UPPER(Master!B22)</f>
         <v>SAMARTHA RAGHAVA NAGABHUSHANAM</v>
       </c>
-      <c r="D37" s="56" t="str">
+      <c r="D37" s="57" t="str">
         <f aca="false">UPPER(Master!B26)</f>
         <v>[TO BE PROVIDED]</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="54" t="str">
+      <c r="A38" s="55" t="str">
         <f aca="false">PROPER(Master!B14)</f>
         <v>[To Be Provided]</v>
       </c>
-      <c r="B38" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D38" s="57" t="str">
+      <c r="B38" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D38" s="58" t="str">
         <f aca="false">B38</f>
         <v>Designated Partner</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="58" t="str">
+      <c r="A39" s="59" t="str">
         <f aca="false">"Membership No. "&amp;Master!B15</f>
         <v>Membership No. [To be provided]</v>
       </c>
@@ -5308,7 +5846,7 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="58" t="str">
+      <c r="A40" s="59" t="str">
         <f aca="false">"UDIN: "&amp;Master!B18</f>
         <v>UDIN: [To be provided]</v>
       </c>
@@ -5372,8 +5910,8 @@
         <f aca="false">UPPER(Master!B2)</f>
         <v>DAIVBHARATHI TECHNOLOGIES LLP</v>
       </c>
-      <c r="F1" s="35" t="s">
-        <v>221</v>
+      <c r="F1" s="36" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5383,7 +5921,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <f aca="false">Master!B3</f>
         <v>No 63, 1st Floor, 1st Main, 7th Block, Koramangala VI Block, Bangalore 560095</v>
       </c>
@@ -5395,249 +5933,249 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="64"/>
+      <c r="E5" s="65"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="65" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="64" t="str">
+      <c r="A8" s="66" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="65" t="str">
         <f aca="false">Master!B32</f>
         <v>(Amount in ₹ '00)</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="30" t="str">
+      <c r="A9" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="31" t="str">
         <f aca="false">Master!B33</f>
         <v>MARCH 31, 2026</v>
       </c>
-      <c r="E9" s="30" t="str">
+      <c r="E9" s="31" t="str">
         <f aca="false">Master!B34</f>
         <v>MARCH 31, 2025</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="66" t="str">
+      <c r="A11" s="67" t="str">
         <f aca="false">Master!B22</f>
         <v>Samartha Raghava Nagabhushanam</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="41" t="n">
         <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$F11)</f>
         <v>900</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="41" t="n">
         <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$F11)</f>
         <v>900</v>
       </c>
-      <c r="F11" s="35" t="s">
-        <v>59</v>
+      <c r="F11" s="36" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="66" t="str">
+      <c r="A12" s="67" t="str">
         <f aca="false">Master!B26</f>
         <v>[To be provided]</v>
       </c>
-      <c r="D12" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="40" t="n">
+      <c r="D12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="67" t="s">
+      <c r="A13" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D13" s="43" t="n">
         <f aca="false">SUM(D11:D12)</f>
         <v>900</v>
       </c>
-      <c r="E13" s="42" t="n">
+      <c r="E13" s="43" t="n">
         <f aca="false">SUM(E11:E12)</f>
         <v>900</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="65" t="s">
-        <v>225</v>
-      </c>
-      <c r="E15" s="64" t="str">
+      <c r="A15" s="66" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" s="65" t="str">
         <f aca="false">Master!B32</f>
         <v>(Amount in ₹ '00)</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="B16" s="29"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30" t="str">
+      <c r="A16" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="31" t="str">
         <f aca="false">Master!B33</f>
         <v>MARCH 31, 2026</v>
       </c>
-      <c r="E16" s="30" t="str">
+      <c r="E16" s="31" t="str">
         <f aca="false">Master!B34</f>
         <v>MARCH 31, 2025</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="58" t="s">
-        <v>226</v>
-      </c>
-      <c r="D17" s="40" t="n">
+      <c r="A17" s="59" t="s">
+        <v>232</v>
+      </c>
+      <c r="D17" s="41" t="n">
         <f aca="false">E19</f>
         <v>900</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E17" s="41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="58" t="s">
-        <v>227</v>
-      </c>
-      <c r="D18" s="40" t="n">
+      <c r="A18" s="59" t="s">
+        <v>233</v>
+      </c>
+      <c r="D18" s="41" t="n">
         <f aca="false">D19-D17</f>
         <v>0</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E18" s="41" t="n">
         <f aca="false">E19-E17</f>
         <v>900</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="68" t="s">
-        <v>228</v>
-      </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="61" t="n">
+      <c r="A19" s="69" t="s">
+        <v>234</v>
+      </c>
+      <c r="B19" s="69"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="62" t="n">
         <f aca="false">D13</f>
         <v>900</v>
       </c>
-      <c r="E19" s="61" t="n">
+      <c r="E19" s="62" t="n">
         <f aca="false">E13</f>
         <v>900</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="65" t="s">
-        <v>229</v>
+      <c r="A21" s="66" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="69" t="s">
-        <v>230</v>
-      </c>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
+      <c r="A22" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
     </row>
     <row r="23" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="65" t="s">
-        <v>231</v>
+      <c r="A24" s="66" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="70" t="s">
-        <v>165</v>
-      </c>
-      <c r="B25" s="70"/>
-      <c r="C25" s="70"/>
-      <c r="D25" s="71" t="str">
+      <c r="A25" s="71" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" s="71"/>
+      <c r="C25" s="71"/>
+      <c r="D25" s="72" t="str">
         <f aca="false">Master!B33</f>
         <v>MARCH 31, 2026</v>
       </c>
-      <c r="E25" s="71" t="str">
+      <c r="E25" s="72" t="str">
         <f aca="false">Master!B34</f>
         <v>MARCH 31, 2025</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="72"/>
-      <c r="B26" s="72"/>
-      <c r="C26" s="72"/>
-      <c r="D26" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="E26" s="73" t="s">
-        <v>232</v>
+      <c r="A26" s="73"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="74" t="s">
+        <v>238</v>
+      </c>
+      <c r="E26" s="74" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="58" t="str">
+      <c r="A27" s="59" t="str">
         <f aca="false">A11</f>
         <v>Samartha Raghava Nagabhushanam</v>
       </c>
-      <c r="D27" s="40" t="n">
+      <c r="D27" s="41" t="n">
         <f aca="false">D11</f>
         <v>900</v>
       </c>
-      <c r="E27" s="40" t="n">
+      <c r="E27" s="41" t="n">
         <f aca="false">E11</f>
         <v>900</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="58" t="str">
+      <c r="A28" s="59" t="str">
         <f aca="false">A12</f>
         <v>[To be provided]</v>
       </c>
-      <c r="D28" s="40" t="n">
+      <c r="D28" s="41" t="n">
         <f aca="false">D12</f>
         <v>0</v>
       </c>
-      <c r="E28" s="40" t="n">
+      <c r="E28" s="41" t="n">
         <f aca="false">E12</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="74" t="s">
+      <c r="A29" s="75" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="42" t="n">
+      <c r="B29" s="69"/>
+      <c r="C29" s="69"/>
+      <c r="D29" s="43" t="n">
         <f aca="false">SUM(D27:D28)</f>
         <v>900</v>
       </c>
-      <c r="E29" s="42" t="n">
+      <c r="E29" s="43" t="n">
         <f aca="false">SUM(E27:E28)</f>
         <v>900</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="D30" s="75" t="n">
+      <c r="A30" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="D30" s="76" t="n">
         <f aca="false">IF(D29=0,0,D27/D29)</f>
         <v>1</v>
       </c>
-      <c r="E30" s="75" t="n">
+      <c r="E30" s="76" t="n">
         <f aca="false">IF(E29=0,0,E27/E29)</f>
         <v>1</v>
       </c>
@@ -5661,7 +6199,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
@@ -5671,8 +6209,8 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
-        <v>234</v>
+      <c r="A1" s="36" t="s">
+        <v>240</v>
       </c>
       <c r="B1" s="18" t="str">
         <f aca="false">UPPER(Master!B2)</f>
@@ -5686,7 +6224,7 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="29" t="str">
         <f aca="false">Master!B3</f>
         <v>No 63, 1st Floor, 1st Main, 7th Block, Koramangala VI Block, Bangalore 560095</v>
       </c>
@@ -5698,1093 +6236,1123 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E5" s="64" t="str">
+      <c r="E5" s="65" t="str">
         <f aca="false">Master!B32</f>
         <v>(Amount in ₹ '00)</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="D6" s="76" t="str">
+      <c r="B6" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="77" t="str">
         <f aca="false">Master!B33</f>
         <v>MARCH 31, 2026</v>
       </c>
-      <c r="E6" s="76" t="str">
+      <c r="E6" s="77" t="str">
         <f aca="false">Master!B34</f>
         <v>MARCH 31, 2025</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="77" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="78" t="s">
-        <v>161</v>
+      <c r="B8" s="78" t="s">
+        <v>177</v>
+      </c>
+      <c r="C8" s="79" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="79"/>
-      <c r="C10" s="80" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="79"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="80"/>
+      <c r="E10" s="80"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="C11" s="81" t="s">
-        <v>236</v>
-      </c>
-      <c r="D11" s="40" t="n">
+      <c r="A11" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="82" t="s">
+        <v>242</v>
+      </c>
+      <c r="D11" s="41" t="n">
         <f aca="false">-SUMIFS(TB!$G:$G,TB!$I:$I,$A11)</f>
         <v>-11209.1152</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="41" t="n">
         <f aca="false">-SUMIFS(TB!$H:$H,TB!$I:$I,$A11)</f>
         <v>-0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="81" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="40" t="n">
+      <c r="C12" s="82" t="s">
+        <v>243</v>
+      </c>
+      <c r="D12" s="41" t="n">
         <f aca="false">PL!D27</f>
         <v>-20002.3134</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="41" t="n">
         <f aca="false">PL!E27</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="81" t="s">
-        <v>238</v>
-      </c>
-      <c r="D13" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="40" t="n">
+      <c r="C13" s="82" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="81" t="s">
-        <v>239</v>
-      </c>
-      <c r="D14" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="40" t="n">
+      <c r="C14" s="82" t="s">
+        <v>245</v>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="65" t="s">
-        <v>240</v>
-      </c>
-      <c r="D15" s="42" t="n">
+      <c r="C15" s="66" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="43" t="n">
         <f aca="false">D11+D12-D13-D14</f>
         <v>-31211.4286</v>
       </c>
-      <c r="E15" s="42" t="n">
+      <c r="E15" s="43" t="n">
         <f aca="false">E11+E12-E13-E14</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="82"/>
-      <c r="C16" s="82"/>
-      <c r="D16" s="42" t="n">
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="D16" s="43" t="n">
         <f aca="false">D15</f>
         <v>-31211.4286</v>
       </c>
-      <c r="E16" s="42" t="n">
+      <c r="E16" s="43" t="n">
         <f aca="false">E15</f>
         <v>-11209.1152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="77" t="s">
-        <v>177</v>
-      </c>
-      <c r="C18" s="78" t="s">
-        <v>64</v>
+      <c r="B18" s="78" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="79" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="79"/>
-      <c r="C19" s="80" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" s="79"/>
-      <c r="E19" s="79"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="81" t="s">
+        <v>247</v>
+      </c>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="81" t="str">
+      <c r="A20" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="82" t="str">
         <f aca="false">"From partner - "&amp;Master!B22</f>
         <v>From partner - Samartha Raghava Nagabhushanam</v>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="41" t="n">
         <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A20)</f>
         <v>24806.8</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E20" s="41" t="n">
         <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A20)</f>
         <v>7806.8</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="81" t="s">
-        <v>242</v>
-      </c>
-      <c r="D21" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A21)</f>
+      <c r="C21" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="43" t="n">
+        <f aca="false">SUM(D20:D20)</f>
+        <v>24806.8</v>
+      </c>
+      <c r="E21" s="43" t="n">
+        <f aca="false">SUM(E20:E20)</f>
+        <v>7806.8</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="78" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="79" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="80"/>
+      <c r="C24" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24" s="80"/>
+      <c r="E24" s="80"/>
+    </row>
+    <row r="25" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="82" t="s">
+        <v>249</v>
+      </c>
+      <c r="D25" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A25)</f>
         <v>1701.8</v>
       </c>
-      <c r="E21" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A21)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="65" t="s">
+      <c r="E25" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="42" t="n">
-        <f aca="false">SUM(D20:D21)</f>
-        <v>26508.6</v>
-      </c>
-      <c r="E22" s="42" t="n">
-        <f aca="false">SUM(E20:E21)</f>
-        <v>7806.8</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="77" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="78" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="79"/>
-      <c r="C26" s="79" t="s">
-        <v>243</v>
-      </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="35" t="s">
-        <v>244</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="D27" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A27)</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A27)</f>
-        <v>0</v>
-      </c>
-    </row>
+      <c r="D26" s="43" t="n">
+        <f aca="false">SUM(D25:D25)</f>
+        <v>1701.8</v>
+      </c>
+      <c r="E26" s="43" t="n">
+        <f aca="false">SUM(E25:E25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="D28" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A28)</f>
-        <v>5483.2048</v>
-      </c>
-      <c r="E28" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A28)</f>
-        <v>2280</v>
+      <c r="B28" s="78" t="s">
+        <v>187</v>
+      </c>
+      <c r="C28" s="79" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="65" t="s">
+      <c r="B30" s="80"/>
+      <c r="C30" s="80" t="s">
+        <v>250</v>
+      </c>
+      <c r="D30" s="80"/>
+      <c r="E30" s="80"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D31" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A31)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D32" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A32)</f>
+        <v>5483.2048</v>
+      </c>
+      <c r="E32" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A32)</f>
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C34" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="42" t="n">
-        <f aca="false">SUM(D27:D28)</f>
+      <c r="D34" s="43" t="n">
+        <f aca="false">SUM(D31:D32)</f>
         <v>5483.2048</v>
       </c>
-      <c r="E30" s="42" t="n">
-        <f aca="false">SUM(E27:E28)</f>
+      <c r="E34" s="43" t="n">
+        <f aca="false">SUM(E31:E32)</f>
         <v>2280</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="77" t="s">
-        <v>183</v>
-      </c>
-      <c r="C32" s="78" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="79"/>
-      <c r="C33" s="80" t="s">
-        <v>247</v>
-      </c>
-      <c r="D33" s="79"/>
-      <c r="E33" s="79"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="81" t="s">
-        <v>248</v>
-      </c>
-      <c r="D34" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A34)</f>
+    <row r="35" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="78" t="s">
+        <v>189</v>
+      </c>
+      <c r="C36" s="79" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="80"/>
+      <c r="C37" s="81" t="s">
+        <v>254</v>
+      </c>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="82" t="s">
+        <v>255</v>
+      </c>
+      <c r="D38" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A38)</f>
         <v>217.6</v>
       </c>
-      <c r="E34" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A34)</f>
+      <c r="E38" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A38)</f>
         <v>350</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="81" t="s">
-        <v>249</v>
-      </c>
-      <c r="D35" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A35)</f>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="C39" s="82" t="s">
+        <v>256</v>
+      </c>
+      <c r="D39" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A39)</f>
         <v>75.0541</v>
       </c>
-      <c r="E35" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A35)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="18" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="81" t="s">
-        <v>251</v>
-      </c>
-      <c r="D37" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A37)</f>
+      <c r="E39" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A39)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="82" t="s">
+        <v>258</v>
+      </c>
+      <c r="D41" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A41)</f>
         <v>25.9305</v>
       </c>
-      <c r="E37" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A37)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="65" t="s">
+      <c r="E41" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="42" t="n">
-        <f aca="false">SUM(D34:D37)</f>
+      <c r="D43" s="43" t="n">
+        <f aca="false">SUM(D38:D41)</f>
         <v>318.5846</v>
       </c>
-      <c r="E39" s="42" t="n">
-        <f aca="false">SUM(E34:E37)</f>
+      <c r="E43" s="43" t="n">
+        <f aca="false">SUM(E38:E41)</f>
         <v>350</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="77" t="s">
-        <v>192</v>
-      </c>
-      <c r="C41" s="78" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="79"/>
-      <c r="C42" s="79"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="79"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="C43" s="81" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A43)</f>
+    <row r="44" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="78" t="s">
+        <v>198</v>
+      </c>
+      <c r="C45" s="79" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="80"/>
+      <c r="C46" s="80"/>
+      <c r="D46" s="80"/>
+      <c r="E46" s="80"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="36" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="82" t="s">
+        <v>121</v>
+      </c>
+      <c r="D47" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A47)</f>
         <v>207.542</v>
       </c>
-      <c r="E43" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A43)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="C44" s="81" t="s">
-        <v>252</v>
-      </c>
-      <c r="D44" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A44)</f>
-        <v>0</v>
-      </c>
-      <c r="E44" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A44)</f>
+      <c r="E47" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="36" t="s">
+        <v>125</v>
+      </c>
+      <c r="C48" s="82" t="s">
+        <v>259</v>
+      </c>
+      <c r="D48" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A48)</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A48)</f>
         <v>127.6848</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="65" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C49" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D45" s="42" t="n">
-        <f aca="false">SUM(D43:D44)</f>
+      <c r="D49" s="43" t="n">
+        <f aca="false">SUM(D47:D48)</f>
         <v>207.542</v>
       </c>
-      <c r="E45" s="42" t="n">
-        <f aca="false">SUM(E43:E44)</f>
+      <c r="E49" s="43" t="n">
+        <f aca="false">SUM(E47:E48)</f>
         <v>127.6848</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="77" t="s">
-        <v>194</v>
-      </c>
-      <c r="C47" s="78" t="s">
+    <row r="50" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="78" t="s">
+        <v>200</v>
+      </c>
+      <c r="C51" s="79" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="80"/>
+      <c r="C52" s="81" t="s">
+        <v>260</v>
+      </c>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="C53" s="82" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="79"/>
-      <c r="C48" s="80" t="s">
-        <v>253</v>
-      </c>
-      <c r="D48" s="79"/>
-      <c r="E48" s="79"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="81" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A49)</f>
-        <v>150</v>
-      </c>
-      <c r="E49" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A49)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="C50" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="D50" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A50)</f>
-        <v>200</v>
-      </c>
-      <c r="E50" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A50)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="81" t="s">
-        <v>110</v>
-      </c>
-      <c r="D51" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A51)</f>
-        <v>1210</v>
-      </c>
-      <c r="E51" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A51)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="C52" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="D52" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A52)</f>
-        <v>25</v>
-      </c>
-      <c r="E52" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A52)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="35" t="s">
-        <v>115</v>
-      </c>
-      <c r="C53" s="81" t="s">
-        <v>114</v>
-      </c>
-      <c r="D53" s="40" t="n">
+      <c r="D53" s="41" t="n">
         <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A53)</f>
         <v>150</v>
       </c>
-      <c r="E53" s="40" t="n">
+      <c r="E53" s="41" t="n">
         <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A53)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="82" t="s">
+        <v>111</v>
+      </c>
+      <c r="D54" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A54)</f>
+        <v>200</v>
+      </c>
+      <c r="E54" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A54)</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="65" t="s">
+      <c r="A55" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="C55" s="82" t="s">
+        <v>113</v>
+      </c>
+      <c r="D55" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A55)</f>
+        <v>1210</v>
+      </c>
+      <c r="E55" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A55)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" s="82" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A56)</f>
+        <v>25</v>
+      </c>
+      <c r="E56" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A56)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="82" t="s">
+        <v>117</v>
+      </c>
+      <c r="D57" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A57)</f>
+        <v>150</v>
+      </c>
+      <c r="E57" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C59" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D55" s="42" t="n">
-        <f aca="false">SUM(D49:D53)</f>
+      <c r="D59" s="43" t="n">
+        <f aca="false">SUM(D53:D57)</f>
         <v>1735</v>
       </c>
-      <c r="E55" s="42" t="n">
-        <f aca="false">SUM(E49:E53)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="77" t="s">
-        <v>196</v>
-      </c>
-      <c r="C57" s="78" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="79"/>
-      <c r="C58" s="80" t="s">
-        <v>254</v>
-      </c>
-      <c r="D58" s="79"/>
-      <c r="E58" s="79"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="35" t="s">
+      <c r="E59" s="43" t="n">
+        <f aca="false">SUM(E53:E57)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="78" t="s">
+        <v>202</v>
+      </c>
+      <c r="C61" s="79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="80"/>
+      <c r="C62" s="81" t="s">
+        <v>261</v>
+      </c>
+      <c r="D62" s="80"/>
+      <c r="E62" s="80"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="82" t="s">
+        <v>262</v>
+      </c>
+      <c r="D63" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A63)</f>
+        <v>28.2094</v>
+      </c>
+      <c r="E63" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="C59" s="81" t="s">
-        <v>255</v>
-      </c>
-      <c r="D59" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A59)</f>
+      <c r="C64" s="82" t="s">
+        <v>263</v>
+      </c>
+      <c r="D64" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A64)</f>
         <v>28.2094</v>
       </c>
-      <c r="E59" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A59)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" s="81" t="s">
-        <v>256</v>
-      </c>
-      <c r="D60" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A60)</f>
-        <v>28.2094</v>
-      </c>
-      <c r="E60" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C62" s="65" t="s">
+      <c r="E64" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A64)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C66" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D62" s="42" t="n">
-        <f aca="false">SUM(D59:D60)</f>
+      <c r="D66" s="43" t="n">
+        <f aca="false">SUM(D63:D64)</f>
         <v>56.4188</v>
       </c>
-      <c r="E62" s="42" t="n">
-        <f aca="false">SUM(E59:E60)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="77" t="s">
-        <v>204</v>
-      </c>
-      <c r="C64" s="78" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="79"/>
-      <c r="C65" s="79"/>
-      <c r="D65" s="79"/>
-      <c r="E65" s="79"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="C66" s="81" t="s">
-        <v>125</v>
-      </c>
-      <c r="D66" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A66)</f>
-        <v>10593.6354</v>
-      </c>
-      <c r="E66" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A66)</f>
+      <c r="E66" s="43" t="n">
+        <f aca="false">SUM(E63:E64)</f>
         <v>0</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C68" s="65" t="s">
+      <c r="B68" s="78" t="s">
+        <v>210</v>
+      </c>
+      <c r="C68" s="79" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="80"/>
+      <c r="C69" s="80"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="80"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C70" s="82" t="s">
+        <v>264</v>
+      </c>
+      <c r="D70" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A70)</f>
+        <v>10593.6354</v>
+      </c>
+      <c r="E70" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A70)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C72" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D68" s="42" t="n">
-        <f aca="false">SUM(D66:D66)</f>
+      <c r="D72" s="43" t="n">
+        <f aca="false">SUM(D70:D70)</f>
         <v>10593.6354</v>
       </c>
-      <c r="E68" s="42" t="n">
-        <f aca="false">SUM(E66:E66)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="77" t="s">
-        <v>209</v>
-      </c>
-      <c r="C70" s="78" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B71" s="79"/>
-      <c r="C71" s="79"/>
-      <c r="D71" s="79"/>
-      <c r="E71" s="79"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C72" s="81" t="s">
-        <v>257</v>
-      </c>
-      <c r="D72" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A72)</f>
+      <c r="E72" s="43" t="n">
+        <f aca="false">SUM(E70:E70)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="78" t="s">
+        <v>215</v>
+      </c>
+      <c r="C74" s="79" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="80"/>
+      <c r="C75" s="80"/>
+      <c r="D75" s="80"/>
+      <c r="E75" s="80"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" s="82" t="s">
+        <v>265</v>
+      </c>
+      <c r="D76" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A76)</f>
         <v>175.1</v>
       </c>
-      <c r="E72" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A72)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C73" s="81" t="s">
-        <v>258</v>
-      </c>
-      <c r="D73" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A73)</f>
+      <c r="E76" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A76)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C77" s="82" t="s">
+        <v>266</v>
+      </c>
+      <c r="D77" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A77)</f>
         <v>4106.8535</v>
       </c>
-      <c r="E73" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A73)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C74" s="81" t="s">
-        <v>132</v>
-      </c>
-      <c r="D74" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A74)</f>
+      <c r="E77" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A77)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C78" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="D78" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A78)</f>
         <v>8.8063</v>
       </c>
-      <c r="E74" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A74)</f>
+      <c r="E78" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A78)</f>
         <v>3.1152</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C75" s="81" t="s">
-        <v>133</v>
-      </c>
-      <c r="D75" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A75)</f>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="C79" s="82" t="s">
+        <v>136</v>
+      </c>
+      <c r="D79" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A79)</f>
         <v>191</v>
       </c>
-      <c r="E75" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A75)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="35" t="s">
-        <v>134</v>
-      </c>
-      <c r="C76" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="D76" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A76)</f>
+      <c r="E79" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A79)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="C80" s="82" t="s">
+        <v>137</v>
+      </c>
+      <c r="D80" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A80)</f>
         <v>253.73</v>
       </c>
-      <c r="E76" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A76)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C77" s="81" t="s">
-        <v>135</v>
-      </c>
-      <c r="D77" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A77)</f>
+      <c r="E80" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A80)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="C81" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="D81" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A81)</f>
         <v>262.2364</v>
       </c>
-      <c r="E77" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A77)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="C78" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="D78" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A78)</f>
+      <c r="E81" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A81)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C82" s="82" t="s">
+        <v>139</v>
+      </c>
+      <c r="D82" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A82)</f>
         <v>700</v>
       </c>
-      <c r="E78" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A78)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="C79" s="81" t="s">
-        <v>137</v>
-      </c>
-      <c r="D79" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A79)</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A79)</f>
+      <c r="E82" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A82)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="C83" s="82" t="s">
+        <v>140</v>
+      </c>
+      <c r="D83" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A83)</f>
+        <v>0</v>
+      </c>
+      <c r="E83" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A83)</f>
         <v>25</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="C80" s="81" t="s">
-        <v>259</v>
-      </c>
-      <c r="D80" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A80)</f>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="C84" s="82" t="s">
+        <v>267</v>
+      </c>
+      <c r="D84" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A84)</f>
         <v>0.2</v>
       </c>
-      <c r="E80" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A80)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="C81" s="81" t="s">
-        <v>139</v>
-      </c>
-      <c r="D81" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A81)</f>
+      <c r="E84" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A84)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="C85" s="82" t="s">
+        <v>142</v>
+      </c>
+      <c r="D85" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A85)</f>
         <v>21.64</v>
       </c>
-      <c r="E81" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A81)</f>
+      <c r="E85" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A85)</f>
         <v>7.8</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="C82" s="81" t="s">
-        <v>140</v>
-      </c>
-      <c r="D82" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A82)</f>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="C86" s="82" t="s">
+        <v>143</v>
+      </c>
+      <c r="D86" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A86)</f>
         <v>120</v>
       </c>
-      <c r="E82" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A82)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="C83" s="81" t="s">
-        <v>141</v>
-      </c>
-      <c r="D83" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A83)</f>
+      <c r="E86" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A86)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C87" s="82" t="s">
+        <v>144</v>
+      </c>
+      <c r="D87" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A87)</f>
         <v>1774.17</v>
       </c>
-      <c r="E83" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A83)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="C84" s="81" t="s">
-        <v>260</v>
-      </c>
-      <c r="D84" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A84)</f>
+      <c r="E87" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A87)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="C88" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="D88" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A88)</f>
         <v>98.7195</v>
       </c>
-      <c r="E84" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A84)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="C85" s="81" t="s">
-        <v>143</v>
-      </c>
-      <c r="D85" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A85)</f>
+      <c r="E88" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A88)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="C89" s="82" t="s">
+        <v>146</v>
+      </c>
+      <c r="D89" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A89)</f>
         <v>805.18</v>
       </c>
-      <c r="E85" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A85)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="C86" s="81" t="s">
-        <v>261</v>
-      </c>
-      <c r="D86" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A86)</f>
+      <c r="E89" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A89)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="36" t="s">
+        <v>147</v>
+      </c>
+      <c r="C90" s="82" t="s">
+        <v>269</v>
+      </c>
+      <c r="D90" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A90)</f>
         <v>25.3568</v>
       </c>
-      <c r="E86" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A86)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="C87" s="81" t="s">
-        <v>262</v>
-      </c>
-      <c r="D87" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A87)</f>
+      <c r="E90" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A90)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="C91" s="82" t="s">
+        <v>270</v>
+      </c>
+      <c r="D91" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A91)</f>
         <v>249.0109</v>
       </c>
-      <c r="E87" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A87)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="35" t="s">
-        <v>146</v>
-      </c>
-      <c r="C88" s="81" t="s">
-        <v>146</v>
-      </c>
-      <c r="D88" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A88)</f>
+      <c r="E91" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A91)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="C92" s="82" t="s">
+        <v>149</v>
+      </c>
+      <c r="D92" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A92)</f>
         <v>9591.275</v>
       </c>
-      <c r="E88" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A88)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="35" t="s">
-        <v>147</v>
-      </c>
-      <c r="C89" s="81" t="s">
-        <v>147</v>
-      </c>
-      <c r="D89" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A89)</f>
+      <c r="E92" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="C93" s="82" t="s">
+        <v>150</v>
+      </c>
+      <c r="D93" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A93)</f>
         <v>245.38</v>
       </c>
-      <c r="E89" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A89)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="C90" s="81" t="s">
-        <v>263</v>
-      </c>
-      <c r="D90" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A90)</f>
+      <c r="E93" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A93)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="C94" s="82" t="s">
+        <v>271</v>
+      </c>
+      <c r="D94" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A94)</f>
         <v>360</v>
       </c>
-      <c r="E90" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A90)</f>
+      <c r="E94" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A94)</f>
         <v>4793.2</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="C91" s="81" t="s">
-        <v>149</v>
-      </c>
-      <c r="D91" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A91)</f>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" s="82" t="s">
+        <v>152</v>
+      </c>
+      <c r="D95" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A95)</f>
         <v>430.36</v>
       </c>
-      <c r="E91" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A91)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="35" t="s">
+      <c r="E95" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A95)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="C96" s="82" t="s">
+        <v>153</v>
+      </c>
+      <c r="D96" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A96)</f>
+        <v>10082.52</v>
+      </c>
+      <c r="E96" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A96)</f>
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="C97" s="82" t="s">
+        <v>272</v>
+      </c>
+      <c r="D97" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A97)</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A97)</f>
+        <v>350</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C98" s="82" t="s">
+        <v>155</v>
+      </c>
+      <c r="D98" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A98)</f>
+        <v>0.0004</v>
+      </c>
+      <c r="E98" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A98)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C99" s="82" t="s">
+        <v>156</v>
+      </c>
+      <c r="D99" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A99)</f>
+        <v>76.81</v>
+      </c>
+      <c r="E99" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A99)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="36" t="s">
+        <v>157</v>
+      </c>
+      <c r="C100" s="82" t="s">
+        <v>273</v>
+      </c>
+      <c r="D100" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A100)</f>
+        <v>240</v>
+      </c>
+      <c r="E100" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A100)</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="36" t="s">
+        <v>158</v>
+      </c>
+      <c r="C101" s="82" t="s">
+        <v>274</v>
+      </c>
+      <c r="D101" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A101)</f>
         <v>150</v>
       </c>
-      <c r="C92" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="D92" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A92)</f>
-        <v>10082.52</v>
-      </c>
-      <c r="E92" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A92)</f>
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="C93" s="81" t="s">
-        <v>264</v>
-      </c>
-      <c r="D93" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A93)</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A93)</f>
-        <v>350</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="C94" s="81" t="s">
-        <v>152</v>
-      </c>
-      <c r="D94" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A94)</f>
-        <v>0.0004</v>
-      </c>
-      <c r="E94" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A94)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="C95" s="81" t="s">
-        <v>153</v>
-      </c>
-      <c r="D95" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A95)</f>
-        <v>76.81</v>
-      </c>
-      <c r="E95" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A95)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="C96" s="81" t="s">
-        <v>265</v>
-      </c>
-      <c r="D96" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A96)</f>
-        <v>240</v>
-      </c>
-      <c r="E96" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A96)</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="C97" s="81" t="s">
-        <v>266</v>
-      </c>
-      <c r="D97" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A97)</f>
-        <v>150</v>
-      </c>
-      <c r="E97" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A97)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="C98" s="81" t="s">
-        <v>156</v>
-      </c>
-      <c r="D98" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A98)</f>
+      <c r="E101" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="C102" s="82" t="s">
+        <v>159</v>
+      </c>
+      <c r="D102" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A102)</f>
         <v>527.6</v>
       </c>
-      <c r="E98" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A98)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="C99" s="81" t="s">
-        <v>267</v>
-      </c>
-      <c r="D99" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A99)</f>
+      <c r="E102" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A102)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="36" t="s">
+        <v>160</v>
+      </c>
+      <c r="C103" s="82" t="s">
+        <v>275</v>
+      </c>
+      <c r="D103" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$G:$G,TB!$I:$I,$A103)</f>
         <v>100</v>
       </c>
-      <c r="E99" s="40" t="n">
-        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A99)</f>
+      <c r="E103" s="41" t="n">
+        <f aca="false">SUMIFS(TB!$H:$H,TB!$I:$I,$A103)</f>
         <v>1250</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="101" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="102" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="103" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="104" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C105" s="65" t="s">
+    <row r="105" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="106" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="107" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="108" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C109" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D105" s="42" t="n">
-        <f aca="false">SUM(D72:D99)</f>
+      <c r="D109" s="43" t="n">
+        <f aca="false">SUM(D76:D103)</f>
         <v>30595.9488</v>
       </c>
-      <c r="E105" s="42" t="n">
-        <f aca="false">SUM(E72:E99)</f>
+      <c r="E109" s="43" t="n">
+        <f aca="false">SUM(E76:E103)</f>
         <v>11209.1152</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="110" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6794,7 +7362,7 @@
     <oddFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="69" man="true" max="16383" min="0"/>
+    <brk id="73" man="true" max="16383" min="0"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -6804,7 +7372,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.4"/>
@@ -6816,87 +7384,87 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="str">
-        <f aca="false">'2.2 - 2.10'!B1</f>
+        <f aca="false">'2.2 - 2.11'!B1</f>
         <v>DAIVBHARATHI TECHNOLOGIES LLP</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="18" t="str">
-        <f aca="false">'2.2 - 2.10'!B2</f>
+        <f aca="false">'2.2 - 2.11'!B2</f>
         <v>LLPIN: [TO BE PROVIDED]</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="28" t="str">
+      <c r="A3" s="29" t="str">
         <f aca="false">Master!B3</f>
         <v>No 63, 1st Floor, 1st Main, 7th Block, Koramangala VI Block, Bangalore 560095</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="18" t="str">
-        <f aca="false">'2.2 - 2.10'!B4</f>
+        <f aca="false">'2.2 - 2.11'!B4</f>
         <v>2. NOTES FORMING PART OF THE FINANCIAL STATEMENTS FOR THE YEAR ENDED MARCH 31, 2026</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="83" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="83"/>
+      <c r="A6" s="84" t="s">
+        <v>276</v>
+      </c>
+      <c r="B6" s="84"/>
     </row>
     <row r="7" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="18" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="84" t="s">
-        <v>270</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="85" t="s">
-        <v>272</v>
-      </c>
-      <c r="E10" s="68"/>
+      <c r="A10" s="85" t="s">
+        <v>278</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>279</v>
+      </c>
+      <c r="C10" s="69"/>
+      <c r="D10" s="86" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" s="69"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="86" t="n">
+      <c r="A11" s="87" t="n">
         <v>1</v>
       </c>
-      <c r="B11" s="58" t="str">
+      <c r="B11" s="59" t="str">
         <f aca="false">Master!B22</f>
         <v>Samartha Raghava Nagabhushanam</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="87" t="n">
+      <c r="A12" s="88" t="n">
         <f aca="false">+A11+1</f>
         <v>2</v>
       </c>
-      <c r="B12" s="82" t="str">
+      <c r="B12" s="83" t="str">
         <f aca="false">Master!B26</f>
         <v>[To be provided]</v>
       </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="88" t="s">
-        <v>201</v>
-      </c>
-      <c r="E12" s="82"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="89" t="s">
+        <v>207</v>
+      </c>
+      <c r="E12" s="83"/>
     </row>
     <row r="13" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="89" t="s">
-        <v>273</v>
-      </c>
-      <c r="E14" s="90" t="str">
+      <c r="A14" s="90" t="s">
+        <v>281</v>
+      </c>
+      <c r="E14" s="28" t="str">
         <f aca="false">Master!B32</f>
         <v>(Amount in ₹ '00)</v>
       </c>
@@ -6904,23 +7472,23 @@
     <row r="15" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="91" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B16" s="91" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" s="79"/>
+        <v>283</v>
+      </c>
+      <c r="C16" s="80"/>
       <c r="D16" s="92" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E16" s="92" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="82"/>
-      <c r="B17" s="82"/>
-      <c r="C17" s="82"/>
+      <c r="A17" s="83"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="83"/>
       <c r="D17" s="93" t="str">
         <f aca="false">PROPER(Master!B33)</f>
         <v>March 31, 2026</v>
@@ -6935,7 +7503,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6958,7 +7526,7 @@
         <v>2</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6967,160 +7535,180 @@
         <v>Samartha Raghava Nagabhushanam</v>
       </c>
       <c r="D22" s="96" t="n">
-        <f aca="false">'2.2 - 2.10'!D20</f>
+        <f aca="false">'2.2 - 2.11'!D20</f>
         <v>24806.8</v>
       </c>
       <c r="E22" s="96" t="n">
-        <f aca="false">'2.2 - 2.10'!E20</f>
+        <f aca="false">'2.2 - 2.11'!E20</f>
         <v>7806.8</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="94" t="n">
         <v>3</v>
       </c>
       <c r="B24" s="97" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="82"/>
-      <c r="B25" s="98" t="str">
+      <c r="B25" s="95" t="str">
         <f aca="false">B11</f>
         <v>Samartha Raghava Nagabhushanam</v>
       </c>
-      <c r="C25" s="82"/>
-      <c r="D25" s="99" t="n">
-        <f aca="false">D22-E22</f>
+      <c r="D25" s="96" t="n">
+        <f aca="false">1700000/Master!$B$31</f>
         <v>17000</v>
       </c>
-      <c r="E25" s="99" t="n">
-        <f aca="false">E22-0</f>
+      <c r="E25" s="96" t="n">
+        <f aca="false">E22</f>
         <v>7806.8</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="27" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="100" t="s">
-        <v>280</v>
-      </c>
-      <c r="B27" s="100"/>
-      <c r="C27" s="100"/>
-      <c r="D27" s="100"/>
-      <c r="E27" s="100"/>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="97" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="83"/>
+      <c r="B27" s="98" t="str">
+        <f aca="false">B11</f>
+        <v>Samartha Raghava Nagabhushanam</v>
+      </c>
+      <c r="C27" s="83"/>
+      <c r="D27" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>281</v>
-      </c>
-      <c r="B29" s="8"/>
-    </row>
-    <row r="30" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="101" t="s">
-        <v>282</v>
-      </c>
-      <c r="B30" s="101"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="101"/>
-      <c r="E30" s="101"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="str">
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="100" t="s">
+        <v>289</v>
+      </c>
+      <c r="B29" s="100"/>
+      <c r="C29" s="100"/>
+      <c r="D29" s="100"/>
+      <c r="E29" s="100"/>
+    </row>
+    <row r="30" customFormat="false" ht="4.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="B31" s="8"/>
+    </row>
+    <row r="32" customFormat="false" ht="33" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="101" t="s">
+        <v>291</v>
+      </c>
+      <c r="B32" s="101"/>
+      <c r="C32" s="101"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="101"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="str">
         <f aca="false">"For "&amp;Master!B16</f>
         <v>For [To be provided]</v>
       </c>
-      <c r="C33" s="7" t="str">
+      <c r="C35" s="7" t="str">
         <f aca="false">Master!B2</f>
         <v>Daivbharathi Technologies LLP</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="54" t="str">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="55" t="str">
         <f aca="false">"(FRN: "&amp;Master!B17&amp;")"</f>
         <v>(FRN: [To be provided])</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="102" t="str">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="102" t="str">
         <f aca="false">UPPER(Master!B13)</f>
         <v>[TO BE PROVIDED]</v>
       </c>
-      <c r="C38" s="56" t="str">
+      <c r="C40" s="57" t="str">
         <f aca="false">UPPER(Master!B22)</f>
         <v>SAMARTHA RAGHAVA NAGABHUSHANAM</v>
       </c>
-      <c r="D38" s="56" t="str">
+      <c r="D40" s="57" t="str">
         <f aca="false">UPPER(Master!B26)</f>
         <v>[TO BE PROVIDED]</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="54" t="str">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="55" t="str">
         <f aca="false">PROPER(Master!B14)</f>
         <v>[To Be Provided]</v>
       </c>
-      <c r="C39" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="D39" s="57" t="str">
-        <f aca="false">C39</f>
+      <c r="C41" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" s="58" t="str">
+        <f aca="false">C41</f>
         <v>Designated Partner</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="58" t="str">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="59" t="str">
         <f aca="false">"Membership No. "&amp;Master!B15</f>
         <v>Membership No. [To be provided]</v>
       </c>
-      <c r="C40" s="2" t="str">
+      <c r="C42" s="2" t="str">
         <f aca="false">"DPIN: "&amp;Master!B23</f>
         <v>DPIN: [To be provided]</v>
       </c>
-      <c r="D40" s="2" t="str">
+      <c r="D42" s="2" t="str">
         <f aca="false">"DPIN: "&amp;Master!B27</f>
         <v>DPIN: [To be provided]</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="58" t="str">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="59" t="str">
         <f aca="false">"UDIN: "&amp;Master!B18</f>
         <v>UDIN: [To be provided]</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="str">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="str">
         <f aca="false">Master!B19</f>
         <v>[To be provided]</v>
       </c>
-      <c r="C42" s="2" t="str">
+      <c r="C44" s="2" t="str">
         <f aca="false">Master!B24</f>
         <v>[To be provided]</v>
       </c>
-      <c r="D42" s="2" t="str">
+      <c r="D44" s="2" t="str">
         <f aca="false">Master!B28</f>
         <v>[To be provided]</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="str">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="str">
         <f aca="false">Master!B20</f>
         <v>[To be provided]</v>
       </c>
-      <c r="C43" s="2" t="str">
+      <c r="C45" s="2" t="str">
         <f aca="false">Master!B25</f>
         <v>[To be provided]</v>
       </c>
-      <c r="D43" s="2" t="str">
+      <c r="D45" s="2" t="str">
         <f aca="false">Master!B29</f>
         <v>[To be provided]</v>
       </c>
@@ -7128,9 +7716,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A32:E32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7147,7 +7735,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7158,7 +7746,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="18" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7169,58 +7757,58 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="103" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B4" s="103" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C4" s="103" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="D4" s="103" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="104" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="105" t="s">
-        <v>6</v>
+        <v>297</v>
       </c>
       <c r="C5" s="106" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D5" s="106" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="104" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="105" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="C6" s="106" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="D6" s="106" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="120" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="104" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="105" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C7" s="106" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D7" s="106" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7228,27 +7816,27 @@
         <v>4</v>
       </c>
       <c r="B8" s="105" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="C8" s="106" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="D8" s="106" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="105" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="104" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="105" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C9" s="106" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="D9" s="106" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7256,27 +7844,27 @@
         <v>6</v>
       </c>
       <c r="B10" s="105" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C10" s="106" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="D10" s="106" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="104" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="105" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
       <c r="C11" s="106" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D11" s="106" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7284,83 +7872,83 @@
         <v>8</v>
       </c>
       <c r="B12" s="105" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C12" s="106" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D12" s="106" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="104" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="105" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C13" s="106" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D13" s="106" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="104" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="105" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C14" s="106" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D14" s="106" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="104" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="105" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C15" s="106" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D15" s="106" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="104" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="105" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C16" s="106" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D16" s="106" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="150" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="104" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="105" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C17" s="106" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D17" s="106" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7368,13 +7956,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="105" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C18" s="106" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="D18" s="106" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7382,83 +7970,111 @@
         <v>15</v>
       </c>
       <c r="B19" s="105" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C19" s="106" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D19" s="106" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="104" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="105" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="C20" s="106" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="D20" s="106" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="104" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="105" t="s">
-        <v>116</v>
+        <v>345</v>
       </c>
       <c r="C21" s="106" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D21" s="106" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="104" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="105" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C22" s="106" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D22" s="106" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="104" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="105" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C23" s="106" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D23" s="106" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="104" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="105" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C24" s="106" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D24" s="106" t="s">
-        <v>344</v>
+        <v>356</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="104" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="105" t="s">
+        <v>357</v>
+      </c>
+      <c r="C25" s="106" t="s">
+        <v>358</v>
+      </c>
+      <c r="D25" s="106" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="104" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="105" t="s">
+        <v>360</v>
+      </c>
+      <c r="C26" s="106" t="s">
+        <v>361</v>
+      </c>
+      <c r="D26" s="106" t="s">
+        <v>362</v>
       </c>
     </row>
   </sheetData>
